--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\2026-04-28\files-mentioned-by-the-user-xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C92529-92F6-456B-8289-D7B653B8039B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745EF726-A7FE-4F18-B71A-5646FDD4F011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7279,31 +7279,31 @@
       </c>
       <c r="B324" s="4">
         <f t="shared" ref="B324" si="209">B$246+G324</f>
-        <v>0.2379</v>
+        <v>0.23530000000000001</v>
       </c>
       <c r="C324" s="7">
         <f t="shared" ref="C324" si="210">C$246+H324</f>
-        <v>0.16010000000000002</v>
+        <v>0.15360000000000001</v>
       </c>
       <c r="D324" s="7">
         <f t="shared" ref="D324" si="211">D$246+I324</f>
-        <v>0.1323</v>
+        <v>0.13</v>
       </c>
       <c r="E324" s="4">
         <f t="shared" ref="E324" si="212">E$246+J324</f>
-        <v>1.9699999999999999E-2</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="G324" s="10">
-        <v>6.8000000000000005E-2</v>
+        <v>6.54E-2</v>
       </c>
       <c r="H324" s="10">
-        <v>4.4200000000000003E-2</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="I324" s="10">
-        <v>1.26E-2</v>
+        <v>1.03E-2</v>
       </c>
       <c r="J324" s="10">
-        <v>1.9699999999999999E-2</v>
+        <v>1.7299999999999999E-2</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745EF726-A7FE-4F18-B71A-5646FDD4F011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA89E2D-D9E7-4082-9D88-3CC90DD2DBB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7307,13 +7307,103 @@
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E325" s="9"/>
+      <c r="A325" s="3">
+        <v>46141</v>
+      </c>
+      <c r="B325" s="4">
+        <f t="shared" ref="B325" si="213">B$246+G325</f>
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="C325" s="7">
+        <f t="shared" ref="C325" si="214">C$246+H325</f>
+        <v>0.15360000000000001</v>
+      </c>
+      <c r="D325" s="7">
+        <f t="shared" ref="D325" si="215">D$246+I325</f>
+        <v>0.13</v>
+      </c>
+      <c r="E325" s="4">
+        <f t="shared" ref="E325" si="216">E$246+J325</f>
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="G325" s="10">
+        <v>6.54E-2</v>
+      </c>
+      <c r="H325" s="10">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="I325" s="10">
+        <v>1.03E-2</v>
+      </c>
+      <c r="J325" s="10">
+        <v>1.7299999999999999E-2</v>
+      </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E326" s="9"/>
+      <c r="A326" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B326" s="4">
+        <f t="shared" ref="B326" si="217">B$246+G326</f>
+        <v>0.2344</v>
+      </c>
+      <c r="C326" s="7">
+        <f t="shared" ref="C326" si="218">C$246+H326</f>
+        <v>0.15229999999999999</v>
+      </c>
+      <c r="D326" s="7">
+        <f t="shared" ref="D326" si="219">D$246+I326</f>
+        <v>0.12990000000000002</v>
+      </c>
+      <c r="E326" s="4">
+        <f t="shared" ref="E326" si="220">E$246+J326</f>
+        <v>1.46E-2</v>
+      </c>
+      <c r="G326" s="10">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="H326" s="10">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="I326" s="10">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="J326" s="10">
+        <v>1.46E-2</v>
+      </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E327" s="9"/>
+      <c r="A327" s="3">
+        <v>46146</v>
+      </c>
+      <c r="B327" s="4">
+        <f t="shared" ref="B327" si="221">B$246+G327</f>
+        <v>0.24109999999999998</v>
+      </c>
+      <c r="C327" s="7">
+        <f t="shared" ref="C327" si="222">C$246+H327</f>
+        <v>0.1643</v>
+      </c>
+      <c r="D327" s="7">
+        <f t="shared" ref="D327" si="223">D$246+I327</f>
+        <v>0.1396</v>
+      </c>
+      <c r="E327" s="4">
+        <f t="shared" ref="E327" si="224">E$246+J327</f>
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="G327" s="10">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="H327" s="10">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="I327" s="10">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="J327" s="10">
+        <v>2.4899999999999999E-2</v>
+      </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E328" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA89E2D-D9E7-4082-9D88-3CC90DD2DBB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A99790-DCC6-4057-9DDF-42950A58512A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7406,7 +7406,37 @@
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E328" s="9"/>
+      <c r="A328" s="3">
+        <v>46148</v>
+      </c>
+      <c r="B328" s="4">
+        <f t="shared" ref="B328" si="225">B$246+G328</f>
+        <v>0.24379999999999999</v>
+      </c>
+      <c r="C328" s="7">
+        <f t="shared" ref="C328" si="226">C$246+H328</f>
+        <v>0.17180000000000001</v>
+      </c>
+      <c r="D328" s="7">
+        <f t="shared" ref="D328" si="227">D$246+I328</f>
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="E328" s="4">
+        <f t="shared" ref="E328" si="228">E$246+J328</f>
+        <v>3.49E-2</v>
+      </c>
+      <c r="G328" s="10">
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="H328" s="10">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="I328" s="10">
+        <v>2.53E-2</v>
+      </c>
+      <c r="J328" s="10">
+        <v>3.49E-2</v>
+      </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E329" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A99790-DCC6-4057-9DDF-42950A58512A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5622A32-3364-4394-AA03-726200238467}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7439,7 +7439,37 @@
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E329" s="9"/>
+      <c r="A329" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B329" s="4">
+        <f t="shared" ref="B329" si="229">B$246+G329</f>
+        <v>0.251</v>
+      </c>
+      <c r="C329" s="7">
+        <f t="shared" ref="C329" si="230">C$246+H329</f>
+        <v>0.18890000000000001</v>
+      </c>
+      <c r="D329" s="7">
+        <f t="shared" ref="D329" si="231">D$246+I329</f>
+        <v>0.1555</v>
+      </c>
+      <c r="E329" s="4">
+        <f t="shared" ref="E329" si="232">E$246+J329</f>
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="G329" s="10">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="H329" s="10">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="I329" s="10">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="J329" s="10">
+        <v>4.5900000000000003E-2</v>
+      </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E330" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5622A32-3364-4394-AA03-726200238467}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B841B7C-8E4F-43C4-85AB-2B806748738E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7472,7 +7472,37 @@
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E330" s="9"/>
+      <c r="A330" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B330" s="4">
+        <f t="shared" ref="B330" si="233">B$246+G330</f>
+        <v>0.24729999999999999</v>
+      </c>
+      <c r="C330" s="7">
+        <f t="shared" ref="C330" si="234">C$246+H330</f>
+        <v>0.18259999999999998</v>
+      </c>
+      <c r="D330" s="7">
+        <f t="shared" ref="D330" si="235">D$246+I330</f>
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="E330" s="4">
+        <f t="shared" ref="E330" si="236">E$246+J330</f>
+        <v>4.53E-2</v>
+      </c>
+      <c r="G330" s="10">
+        <v>7.7399999999999997E-2</v>
+      </c>
+      <c r="H330" s="10">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="I330" s="10">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="J330" s="10">
+        <v>4.53E-2</v>
+      </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E331" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B841B7C-8E4F-43C4-85AB-2B806748738E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9E7B0-37A0-4E56-8013-44763D56675F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7505,7 +7505,37 @@
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E331" s="9"/>
+      <c r="A331" s="3">
+        <v>46153</v>
+      </c>
+      <c r="B331" s="4">
+        <f t="shared" ref="B331" si="237">B$246+G331</f>
+        <v>0.25309999999999999</v>
+      </c>
+      <c r="C331" s="7">
+        <f t="shared" ref="C331" si="238">C$246+H331</f>
+        <v>0.1953</v>
+      </c>
+      <c r="D331" s="7">
+        <f t="shared" ref="D331" si="239">D$246+I331</f>
+        <v>0.15629999999999999</v>
+      </c>
+      <c r="E331" s="4">
+        <f t="shared" ref="E331" si="240">E$246+J331</f>
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="G331" s="10">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="H331" s="10">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="I331" s="10">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="J331" s="10">
+        <v>5.3400000000000003E-2</v>
+      </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E332" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9E7B0-37A0-4E56-8013-44763D56675F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E5545E-839A-4FAB-B62F-2F1704CADD43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7538,7 +7538,37 @@
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E332" s="9"/>
+      <c r="A332" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B332" s="4">
+        <f t="shared" ref="B332" si="241">B$246+G332</f>
+        <v>0.25529999999999997</v>
+      </c>
+      <c r="C332" s="7">
+        <f t="shared" ref="C332" si="242">C$246+H332</f>
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="D332" s="7">
+        <f t="shared" ref="D332" si="243">D$246+I332</f>
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="E332" s="4">
+        <f t="shared" ref="E332" si="244">E$246+J332</f>
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="G332" s="10">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="H332" s="10">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="I332" s="10">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="J332" s="10">
+        <v>5.7700000000000001E-2</v>
+      </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E333" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E5545E-839A-4FAB-B62F-2F1704CADD43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABF866-B879-43C0-A3B3-928E3B6A4CDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;₩&quot;* #,##0.00_-;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -95,6 +95,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -127,7 +134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -156,6 +163,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -541,7 +551,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:S372"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -7174,7 +7184,7 @@
         <v>1.52E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:19" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>46135</v>
       </c>
@@ -7206,8 +7216,9 @@
       <c r="J321" s="10">
         <v>1.7600000000000001E-2</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="S321" s="11"/>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>46136</v>
       </c>
@@ -7240,7 +7251,7 @@
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>46139</v>
       </c>
@@ -7273,7 +7284,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>46140</v>
       </c>
@@ -7306,7 +7317,7 @@
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>46141</v>
       </c>
@@ -7339,7 +7350,7 @@
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>46142</v>
       </c>
@@ -7372,7 +7383,7 @@
         <v>1.46E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>46146</v>
       </c>
@@ -7405,7 +7416,7 @@
         <v>2.4899999999999999E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>46148</v>
       </c>
@@ -7438,7 +7449,7 @@
         <v>3.49E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>46149</v>
       </c>
@@ -7471,7 +7482,7 @@
         <v>4.5900000000000003E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>46150</v>
       </c>
@@ -7504,7 +7515,7 @@
         <v>4.53E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>46153</v>
       </c>
@@ -7537,7 +7548,7 @@
         <v>5.3400000000000003E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>46154</v>
       </c>
@@ -7570,16 +7581,46 @@
         <v>5.7700000000000001E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E333" s="9"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A333" s="3">
+        <v>46155</v>
+      </c>
+      <c r="B333" s="4">
+        <f t="shared" ref="B333" si="245">B$246+G333</f>
+        <v>0.25480000000000003</v>
+      </c>
+      <c r="C333" s="7">
+        <f t="shared" ref="C333" si="246">C$246+H333</f>
+        <v>0.1915</v>
+      </c>
+      <c r="D333" s="7">
+        <f t="shared" ref="D333" si="247">D$246+I333</f>
+        <v>0.15460000000000002</v>
+      </c>
+      <c r="E333" s="4">
+        <f t="shared" ref="E333" si="248">E$246+J333</f>
+        <v>6.4199999999999993E-2</v>
+      </c>
+      <c r="G333" s="10">
+        <v>8.4900000000000003E-2</v>
+      </c>
+      <c r="H333" s="10">
+        <v>7.5600000000000001E-2</v>
+      </c>
+      <c r="I333" s="10">
+        <v>3.49E-2</v>
+      </c>
+      <c r="J333" s="10">
+        <v>6.4199999999999993E-2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E334" s="9"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E335" s="9"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E336" s="9"/>
     </row>
     <row r="337" spans="5:5" x14ac:dyDescent="0.3">

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABF866-B879-43C0-A3B3-928E3B6A4CDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78498662-5C40-4C3F-878E-2E7B6E1AC8A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7615,10 +7615,70 @@
       </c>
     </row>
     <row r="334" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="E334" s="9"/>
+      <c r="A334" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B334" s="4">
+        <f t="shared" ref="B334" si="249">B$246+G334</f>
+        <v>0.25669999999999998</v>
+      </c>
+      <c r="C334" s="7">
+        <f t="shared" ref="C334" si="250">C$246+H334</f>
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="D334" s="7">
+        <f t="shared" ref="D334" si="251">D$246+I334</f>
+        <v>0.15820000000000001</v>
+      </c>
+      <c r="E334" s="4">
+        <f t="shared" ref="E334" si="252">E$246+J334</f>
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="G334" s="10">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="H334" s="10">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="I334" s="10">
+        <v>3.85E-2</v>
+      </c>
+      <c r="J334" s="10">
+        <v>6.6699999999999995E-2</v>
+      </c>
     </row>
     <row r="335" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="E335" s="9"/>
+      <c r="A335" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B335" s="4">
+        <f t="shared" ref="B335" si="253">B$246+G335</f>
+        <v>0.25839999999999996</v>
+      </c>
+      <c r="C335" s="7">
+        <f t="shared" ref="C335" si="254">C$246+H335</f>
+        <v>0.2024</v>
+      </c>
+      <c r="D335" s="7">
+        <f t="shared" ref="D335" si="255">D$246+I335</f>
+        <v>0.1595</v>
+      </c>
+      <c r="E335" s="4">
+        <f t="shared" ref="E335" si="256">E$246+J335</f>
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="G335" s="10">
+        <v>8.8499999999999995E-2</v>
+      </c>
+      <c r="H335" s="10">
+        <v>8.6499999999999994E-2</v>
+      </c>
+      <c r="I335" s="10">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="J335" s="10">
+        <v>5.4899999999999997E-2</v>
+      </c>
     </row>
     <row r="336" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E336" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78498662-5C40-4C3F-878E-2E7B6E1AC8A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18383AB2-91CB-4C46-A399-7B73E46ECD68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7681,7 +7681,37 @@
       </c>
     </row>
     <row r="336" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="E336" s="9"/>
+      <c r="A336" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B336" s="4">
+        <f t="shared" ref="B336" si="257">B$246+G336</f>
+        <v>0.247</v>
+      </c>
+      <c r="C336" s="7">
+        <f t="shared" ref="C336" si="258">C$246+H336</f>
+        <v>0.18630000000000002</v>
+      </c>
+      <c r="D336" s="7">
+        <f t="shared" ref="D336" si="259">D$246+I336</f>
+        <v>0.14629999999999999</v>
+      </c>
+      <c r="E336" s="4">
+        <f t="shared" ref="E336" si="260">E$246+J336</f>
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="G336" s="10">
+        <v>7.7100000000000002E-2</v>
+      </c>
+      <c r="H336" s="10">
+        <v>7.0400000000000004E-2</v>
+      </c>
+      <c r="I336" s="10">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="J336" s="10">
+        <v>4.7199999999999999E-2</v>
+      </c>
     </row>
     <row r="337" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E337" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18383AB2-91CB-4C46-A399-7B73E46ECD68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD451B2D-C042-4866-92A5-B095C024FA0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7713,52 +7713,112 @@
         <v>4.7199999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E337" s="9"/>
-    </row>
-    <row r="338" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E338" s="9"/>
-    </row>
-    <row r="339" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A337" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B337" s="4">
+        <f t="shared" ref="B337" si="261">B$246+G337</f>
+        <v>0.24809999999999999</v>
+      </c>
+      <c r="C337" s="7">
+        <f t="shared" ref="C337" si="262">C$246+H337</f>
+        <v>0.18140000000000001</v>
+      </c>
+      <c r="D337" s="7">
+        <f t="shared" ref="D337" si="263">D$246+I337</f>
+        <v>0.1477</v>
+      </c>
+      <c r="E337" s="4">
+        <f t="shared" ref="E337" si="264">E$246+J337</f>
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="G337" s="10">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="H337" s="10">
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="I337" s="10">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J337" s="10">
+        <v>4.6300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A338" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B338" s="4">
+        <f t="shared" ref="B338" si="265">B$246+G338</f>
+        <v>0.2452</v>
+      </c>
+      <c r="C338" s="7">
+        <f t="shared" ref="C338" si="266">C$246+H338</f>
+        <v>0.17610000000000001</v>
+      </c>
+      <c r="D338" s="7">
+        <f t="shared" ref="D338" si="267">D$246+I338</f>
+        <v>0.1434</v>
+      </c>
+      <c r="E338" s="4">
+        <f t="shared" ref="E338" si="268">E$246+J338</f>
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="G338" s="10">
+        <v>7.5300000000000006E-2</v>
+      </c>
+      <c r="H338" s="10">
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="I338" s="10">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="J338" s="10">
+        <v>4.1799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E339" s="9"/>
     </row>
-    <row r="340" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E340" s="9"/>
     </row>
-    <row r="341" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E341" s="9"/>
     </row>
-    <row r="342" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E342" s="9"/>
     </row>
-    <row r="343" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E343" s="9"/>
     </row>
-    <row r="344" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E344" s="9"/>
     </row>
-    <row r="345" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E345" s="9"/>
     </row>
-    <row r="346" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E346" s="9"/>
     </row>
-    <row r="347" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E347" s="9"/>
     </row>
-    <row r="348" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E348" s="9"/>
     </row>
-    <row r="349" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E349" s="9"/>
     </row>
-    <row r="350" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E350" s="9"/>
     </row>
-    <row r="351" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E351" s="9"/>
     </row>
-    <row r="352" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E352" s="9"/>
     </row>
     <row r="353" spans="5:5" x14ac:dyDescent="0.3">

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD451B2D-C042-4866-92A5-B095C024FA0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1077D597-5F40-4E73-A511-90B894C1C011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7780,7 +7780,37 @@
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E339" s="9"/>
+      <c r="A339" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B339" s="4">
+        <f t="shared" ref="B339" si="269">B$246+G339</f>
+        <v>0.25080000000000002</v>
+      </c>
+      <c r="C339" s="7">
+        <f t="shared" ref="C339" si="270">C$246+H339</f>
+        <v>0.18740000000000001</v>
+      </c>
+      <c r="D339" s="7">
+        <f t="shared" ref="D339" si="271">D$246+I339</f>
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="E339" s="4">
+        <f t="shared" ref="E339" si="272">E$246+J339</f>
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="G339" s="10">
+        <v>8.09E-2</v>
+      </c>
+      <c r="H339" s="10">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="I339" s="10">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="J339" s="10">
+        <v>5.6300000000000003E-2</v>
+      </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E340" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1077D597-5F40-4E73-A511-90B894C1C011}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB922AE7-32AD-4EC1-8B73-B742EB9BB7A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7813,7 +7813,37 @@
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E340" s="9"/>
+      <c r="A340" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B340" s="4">
+        <f t="shared" ref="B340" si="273">B$246+G340</f>
+        <v>0.24990000000000001</v>
+      </c>
+      <c r="C340" s="7">
+        <f t="shared" ref="C340" si="274">C$246+H340</f>
+        <v>0.19220000000000001</v>
+      </c>
+      <c r="D340" s="7">
+        <f t="shared" ref="D340" si="275">D$246+I340</f>
+        <v>0.15310000000000001</v>
+      </c>
+      <c r="E340" s="4">
+        <f t="shared" ref="E340" si="276">E$246+J340</f>
+        <v>6.1400000000000003E-2</v>
+      </c>
+      <c r="G340" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="H340" s="10">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="I340" s="10">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="J340" s="10">
+        <v>6.1400000000000003E-2</v>
+      </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E341" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB922AE7-32AD-4EC1-8B73-B742EB9BB7A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA35B5CF-01CD-46B6-B4EA-F393B4A1E173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7846,7 +7846,37 @@
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E341" s="9"/>
+      <c r="A341" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B341" s="4">
+        <f t="shared" ref="B341" si="277">B$246+G341</f>
+        <v>0.25129999999999997</v>
+      </c>
+      <c r="C341" s="7">
+        <f t="shared" ref="C341" si="278">C$246+H341</f>
+        <v>0.19290000000000002</v>
+      </c>
+      <c r="D341" s="7">
+        <f t="shared" ref="D341" si="279">D$246+I341</f>
+        <v>0.15390000000000001</v>
+      </c>
+      <c r="E341" s="4">
+        <f t="shared" ref="E341" si="280">E$246+J341</f>
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="G341" s="10">
+        <v>8.14E-2</v>
+      </c>
+      <c r="H341" s="10">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="I341" s="10">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="J341" s="10">
+        <v>6.6500000000000004E-2</v>
+      </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E342" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA35B5CF-01CD-46B6-B4EA-F393B4A1E173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FA836A-200D-456E-AC3D-4C1139B9C2D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7879,7 +7879,37 @@
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E342" s="9"/>
+      <c r="A342" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B342" s="4">
+        <f t="shared" ref="B342" si="281">B$246+G342</f>
+        <v>0.25540000000000002</v>
+      </c>
+      <c r="C342" s="7">
+        <f t="shared" ref="C342" si="282">C$246+H342</f>
+        <v>0.20779999999999998</v>
+      </c>
+      <c r="D342" s="7">
+        <f t="shared" ref="D342" si="283">D$246+I342</f>
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="E342" s="4">
+        <f t="shared" ref="E342" si="284">E$246+J342</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G342" s="10">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="H342" s="10">
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="I342" s="10">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="J342" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E343" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FA836A-200D-456E-AC3D-4C1139B9C2D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5711BCCF-118C-4291-9F91-049BC67986C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7912,7 +7912,37 @@
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E343" s="9"/>
+      <c r="A343" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B343" s="4">
+        <f t="shared" ref="B343" si="285">B$246+G343</f>
+        <v>0.2535</v>
+      </c>
+      <c r="C343" s="7">
+        <f t="shared" ref="C343" si="286">C$246+H343</f>
+        <v>0.20400000000000001</v>
+      </c>
+      <c r="D343" s="7">
+        <f t="shared" ref="D343" si="287">D$246+I343</f>
+        <v>0.16020000000000001</v>
+      </c>
+      <c r="E343" s="4">
+        <f t="shared" ref="E343" si="288">E$246+J343</f>
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="G343" s="10">
+        <v>8.3599999999999994E-2</v>
+      </c>
+      <c r="H343" s="10">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="I343" s="10">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="J343" s="10">
+        <v>6.6100000000000006E-2</v>
+      </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E344" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5711BCCF-118C-4291-9F91-049BC67986C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77462E3C-06CD-4560-B8F9-B616CA61EFDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7945,10 +7945,70 @@
       </c>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E344" s="9"/>
+      <c r="A344" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B344" s="4">
+        <f t="shared" ref="B344" si="289">B$246+G344</f>
+        <v>0.2576</v>
+      </c>
+      <c r="C344" s="7">
+        <f t="shared" ref="C344" si="290">C$246+H344</f>
+        <v>0.21110000000000001</v>
+      </c>
+      <c r="D344" s="7">
+        <f t="shared" ref="D344" si="291">D$246+I344</f>
+        <v>0.1633</v>
+      </c>
+      <c r="E344" s="4">
+        <f t="shared" ref="E344" si="292">E$246+J344</f>
+        <v>7.7399999999999997E-2</v>
+      </c>
+      <c r="G344" s="10">
+        <v>8.77E-2</v>
+      </c>
+      <c r="H344" s="10">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="I344" s="10">
+        <v>4.36E-2</v>
+      </c>
+      <c r="J344" s="10">
+        <v>7.7399999999999997E-2</v>
+      </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E345" s="9"/>
+      <c r="A345" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B345" s="4">
+        <f t="shared" ref="B345" si="293">B$246+G345</f>
+        <v>0.25729999999999997</v>
+      </c>
+      <c r="C345" s="7">
+        <f t="shared" ref="C345" si="294">C$246+H345</f>
+        <v>0.21340000000000001</v>
+      </c>
+      <c r="D345" s="7">
+        <f t="shared" ref="D345" si="295">D$246+I345</f>
+        <v>0.1633</v>
+      </c>
+      <c r="E345" s="4">
+        <f t="shared" ref="E345" si="296">E$246+J345</f>
+        <v>8.0299999999999996E-2</v>
+      </c>
+      <c r="G345" s="10">
+        <v>8.7400000000000005E-2</v>
+      </c>
+      <c r="H345" s="10">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="I345" s="10">
+        <v>4.36E-2</v>
+      </c>
+      <c r="J345" s="10">
+        <v>8.0299999999999996E-2</v>
+      </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E346" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77462E3C-06CD-4560-B8F9-B616CA61EFDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536662B0-F3D7-4030-B286-24E85BFD11A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8011,7 +8011,37 @@
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E346" s="9"/>
+      <c r="A346" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B346" s="4">
+        <f t="shared" ref="B346" si="297">B$246+G346</f>
+        <v>0.25639999999999996</v>
+      </c>
+      <c r="C346" s="7">
+        <f t="shared" ref="C346" si="298">C$246+H346</f>
+        <v>0.2195</v>
+      </c>
+      <c r="D346" s="7">
+        <f t="shared" ref="D346" si="299">D$246+I346</f>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="E346" s="4">
+        <f t="shared" ref="E346" si="300">E$246+J346</f>
+        <v>8.3099999999999993E-2</v>
+      </c>
+      <c r="G346" s="10">
+        <v>8.6499999999999994E-2</v>
+      </c>
+      <c r="H346" s="10">
+        <v>0.1036</v>
+      </c>
+      <c r="I346" s="10">
+        <v>4.53E-2</v>
+      </c>
+      <c r="J346" s="10">
+        <v>8.3099999999999993E-2</v>
+      </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E347" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536662B0-F3D7-4030-B286-24E85BFD11A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72330DA3-5981-40B0-A2A2-FC5850C302AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8044,16 +8044,136 @@
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E347" s="9"/>
+      <c r="A347" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B347" s="4">
+        <f t="shared" ref="B347" si="301">B$246+G347</f>
+        <v>0.25659999999999999</v>
+      </c>
+      <c r="C347" s="7">
+        <f t="shared" ref="C347" si="302">C$246+H347</f>
+        <v>0.22260000000000002</v>
+      </c>
+      <c r="D347" s="7">
+        <f t="shared" ref="D347" si="303">D$246+I347</f>
+        <v>0.16520000000000001</v>
+      </c>
+      <c r="E347" s="4">
+        <f t="shared" ref="E347" si="304">E$246+J347</f>
+        <v>8.2900000000000001E-2</v>
+      </c>
+      <c r="G347" s="10">
+        <v>8.6699999999999999E-2</v>
+      </c>
+      <c r="H347" s="10">
+        <v>0.1067</v>
+      </c>
+      <c r="I347" s="10">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="J347" s="10">
+        <v>8.2900000000000001E-2</v>
+      </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E348" s="9"/>
+      <c r="A348" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B348" s="4">
+        <f t="shared" ref="B348" si="305">B$246+G348</f>
+        <v>0.2586</v>
+      </c>
+      <c r="C348" s="7">
+        <f t="shared" ref="C348" si="306">C$246+H348</f>
+        <v>0.21810000000000002</v>
+      </c>
+      <c r="D348" s="7">
+        <f t="shared" ref="D348" si="307">D$246+I348</f>
+        <v>0.1663</v>
+      </c>
+      <c r="E348" s="4">
+        <f t="shared" ref="E348" si="308">E$246+J348</f>
+        <v>7.9600000000000004E-2</v>
+      </c>
+      <c r="G348" s="10">
+        <v>8.8700000000000001E-2</v>
+      </c>
+      <c r="H348" s="10">
+        <v>0.1022</v>
+      </c>
+      <c r="I348" s="10">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="J348" s="10">
+        <v>7.9600000000000004E-2</v>
+      </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E349" s="9"/>
+      <c r="A349" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B349" s="4">
+        <f t="shared" ref="B349" si="309">B$246+G349</f>
+        <v>0.23980000000000001</v>
+      </c>
+      <c r="C349" s="7">
+        <f t="shared" ref="C349" si="310">C$246+H349</f>
+        <v>0.18030000000000002</v>
+      </c>
+      <c r="D349" s="7">
+        <f t="shared" ref="D349" si="311">D$246+I349</f>
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="E349" s="4">
+        <f t="shared" ref="E349" si="312">E$246+J349</f>
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="G349" s="10">
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="H349" s="10">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="I349" s="10">
+        <v>1.78E-2</v>
+      </c>
+      <c r="J349" s="10">
+        <v>5.1200000000000002E-2</v>
+      </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E350" s="9"/>
+      <c r="A350" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B350" s="4">
+        <f t="shared" ref="B350" si="313">B$246+G350</f>
+        <v>0.24230000000000002</v>
+      </c>
+      <c r="C350" s="7">
+        <f t="shared" ref="C350" si="314">C$246+H350</f>
+        <v>0.18959999999999999</v>
+      </c>
+      <c r="D350" s="7">
+        <f t="shared" ref="D350" si="315">D$246+I350</f>
+        <v>0.1434</v>
+      </c>
+      <c r="E350" s="4">
+        <f t="shared" ref="E350" si="316">E$246+J350</f>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G350" s="10">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="H350" s="10">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="I350" s="10">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="J350" s="10">
+        <v>6.0999999999999999E-2</v>
+      </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E351" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Desktop\김현수\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72330DA3-5981-40B0-A2A2-FC5850C302AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32087CEF-2A3D-42C5-996D-2B05F17A2CFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8176,10 +8176,70 @@
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E351" s="9"/>
+      <c r="A351" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B351" s="4">
+        <f t="shared" ref="B351" si="317">B$246+G351</f>
+        <v>0.2397</v>
+      </c>
+      <c r="C351" s="7">
+        <f t="shared" ref="C351" si="318">C$246+H351</f>
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="D351" s="7">
+        <f t="shared" ref="D351" si="319">D$246+I351</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E351" s="4">
+        <f t="shared" ref="E351" si="320">E$246+J351</f>
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="G351" s="10">
+        <v>6.9800000000000001E-2</v>
+      </c>
+      <c r="H351" s="10">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="I351" s="10">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="J351" s="10">
+        <v>5.0500000000000003E-2</v>
+      </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E352" s="9"/>
+      <c r="A352" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B352" s="4">
+        <f t="shared" ref="B352" si="321">B$246+G352</f>
+        <v>0.2311</v>
+      </c>
+      <c r="C352" s="7">
+        <f t="shared" ref="C352" si="322">C$246+H352</f>
+        <v>0.1673</v>
+      </c>
+      <c r="D352" s="7">
+        <f t="shared" ref="D352" si="323">D$246+I352</f>
+        <v>0.12940000000000002</v>
+      </c>
+      <c r="E352" s="4">
+        <f t="shared" ref="E352" si="324">E$246+J352</f>
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="G352" s="10">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="H352" s="10">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="I352" s="10">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="J352" s="10">
+        <v>4.4200000000000003E-2</v>
+      </c>
     </row>
     <row r="353" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E353" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32087CEF-2A3D-42C5-996D-2B05F17A2CFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD06F1BB-0705-4257-8B62-7656F9A05596}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8241,52 +8241,82 @@
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
-    <row r="353" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E353" s="9"/>
-    </row>
-    <row r="354" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A353" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B353" s="4">
+        <f t="shared" ref="B353" si="325">B$246+G353</f>
+        <v>0.24340000000000001</v>
+      </c>
+      <c r="C353" s="7">
+        <f t="shared" ref="C353" si="326">C$246+H353</f>
+        <v>0.1913</v>
+      </c>
+      <c r="D353" s="7">
+        <f t="shared" ref="D353" si="327">D$246+I353</f>
+        <v>0.1482</v>
+      </c>
+      <c r="E353" s="4">
+        <f t="shared" ref="E353" si="328">E$246+J353</f>
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="G353" s="10">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="H353" s="10">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="I353" s="10">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="J353" s="10">
+        <v>5.1900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E354" s="9"/>
     </row>
-    <row r="355" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E355" s="9"/>
     </row>
-    <row r="356" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E356" s="9"/>
     </row>
-    <row r="357" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E357" s="9"/>
     </row>
-    <row r="358" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E358" s="9"/>
     </row>
-    <row r="359" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E359" s="9"/>
     </row>
-    <row r="360" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E360" s="9"/>
     </row>
-    <row r="361" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E361" s="9"/>
     </row>
-    <row r="362" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E362" s="9"/>
     </row>
-    <row r="363" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E363" s="9"/>
     </row>
-    <row r="364" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E364" s="9"/>
     </row>
-    <row r="365" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E365" s="9"/>
     </row>
-    <row r="366" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E366" s="9"/>
     </row>
-    <row r="367" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E367" s="9"/>
     </row>
-    <row r="368" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E368" s="9"/>
     </row>
     <row r="369" spans="5:5" x14ac:dyDescent="0.3">

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD06F1BB-0705-4257-8B62-7656F9A05596}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A62C6F-550D-4460-BC2C-B921D28A0DFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8275,7 +8275,37 @@
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E354" s="9"/>
+      <c r="A354" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B354" s="4">
+        <f t="shared" ref="B354" si="329">B$246+G354</f>
+        <v>0.24540000000000001</v>
+      </c>
+      <c r="C354" s="7">
+        <f t="shared" ref="C354" si="330">C$246+H354</f>
+        <v>0.1958</v>
+      </c>
+      <c r="D354" s="7">
+        <f t="shared" ref="D354" si="331">D$246+I354</f>
+        <v>0.15129999999999999</v>
+      </c>
+      <c r="E354" s="4">
+        <f t="shared" ref="E354" si="332">E$246+J354</f>
+        <v>6.1400000000000003E-2</v>
+      </c>
+      <c r="G354" s="10">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="H354" s="10">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="I354" s="10">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="J354" s="10">
+        <v>6.1400000000000003E-2</v>
+      </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E355" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A62C6F-550D-4460-BC2C-B921D28A0DFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7712B8-A986-4EEF-A43D-B927BCB7EAB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7712B8-A986-4EEF-A43D-B927BCB7EAB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC563A7F-6C5A-4906-82F0-BE74E9DE6263}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8308,7 +8308,37 @@
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E355" s="9"/>
+      <c r="A355" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B355" s="4">
+        <f t="shared" ref="B355" si="333">B$246+G355</f>
+        <v>0.25440000000000002</v>
+      </c>
+      <c r="C355" s="7">
+        <f t="shared" ref="C355" si="334">C$246+H355</f>
+        <v>0.2142</v>
+      </c>
+      <c r="D355" s="7">
+        <f t="shared" ref="D355" si="335">D$246+I355</f>
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="E355" s="4">
+        <f t="shared" ref="E355" si="336">E$246+J355</f>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="G355" s="10">
+        <v>8.4500000000000006E-2</v>
+      </c>
+      <c r="H355" s="10">
+        <v>9.8299999999999998E-2</v>
+      </c>
+      <c r="I355" s="10">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="J355" s="10">
+        <v>6.5199999999999994E-2</v>
+      </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E356" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC563A7F-6C5A-4906-82F0-BE74E9DE6263}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C45D3C6-9037-45F4-BD12-2DBB8EF9B879}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C45D3C6-9037-45F4-BD12-2DBB8EF9B879}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A66988-8870-4B76-A051-681B63639EC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A66988-8870-4B76-A051-681B63639EC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258496EB-C0BD-457F-8AB5-C332B318C4E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8341,10 +8341,70 @@
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E356" s="9"/>
+      <c r="A356" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B356" s="4">
+        <f t="shared" ref="B356" si="337">B$246+G356</f>
+        <v>0.25090000000000001</v>
+      </c>
+      <c r="C356" s="7">
+        <f t="shared" ref="C356" si="338">C$246+H356</f>
+        <v>0.20480000000000001</v>
+      </c>
+      <c r="D356" s="7">
+        <f t="shared" ref="D356" si="339">D$246+I356</f>
+        <v>0.15720000000000001</v>
+      </c>
+      <c r="E356" s="4">
+        <f t="shared" ref="E356" si="340">E$246+J356</f>
+        <v>6.59E-2</v>
+      </c>
+      <c r="G356" s="10">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H356" s="10">
+        <v>8.8900000000000007E-2</v>
+      </c>
+      <c r="I356" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="J356" s="10">
+        <v>6.59E-2</v>
+      </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E357" s="9"/>
+      <c r="A357" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B357" s="4">
+        <f t="shared" ref="B357" si="341">B$246+G357</f>
+        <v>0.24659999999999999</v>
+      </c>
+      <c r="C357" s="7">
+        <f t="shared" ref="C357" si="342">C$246+H357</f>
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="D357" s="7">
+        <f t="shared" ref="D357" si="343">D$246+I357</f>
+        <v>0.1492</v>
+      </c>
+      <c r="E357" s="4">
+        <f t="shared" ref="E357" si="344">E$246+J357</f>
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="G357" s="10">
+        <v>7.6700000000000004E-2</v>
+      </c>
+      <c r="H357" s="10">
+        <v>8.7300000000000003E-2</v>
+      </c>
+      <c r="I357" s="10">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="J357" s="10">
+        <v>6.9500000000000006E-2</v>
+      </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E358" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258496EB-C0BD-457F-8AB5-C332B318C4E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184D15FA-A62D-4636-B1C1-CD08F1AE7538}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8407,7 +8407,37 @@
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E358" s="9"/>
+      <c r="A358" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B358" s="4">
+        <f t="shared" ref="B358" si="345">B$246+G358</f>
+        <v>0.24979999999999999</v>
+      </c>
+      <c r="C358" s="7">
+        <f t="shared" ref="C358" si="346">C$246+H358</f>
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="D358" s="7">
+        <f t="shared" ref="D358" si="347">D$246+I358</f>
+        <v>0.15889999999999999</v>
+      </c>
+      <c r="E358" s="4">
+        <f t="shared" ref="E358" si="348">E$246+J358</f>
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="G358" s="10">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="H358" s="10">
+        <v>9.4200000000000006E-2</v>
+      </c>
+      <c r="I358" s="10">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="J358" s="10">
+        <v>7.1099999999999997E-2</v>
+      </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E359" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184D15FA-A62D-4636-B1C1-CD08F1AE7538}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20220998-5FBA-4CD0-8259-3A1971D89802}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8440,25 +8440,235 @@
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E359" s="9"/>
+      <c r="A359" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B359" s="4">
+        <f t="shared" ref="B359" si="349">B$246+G359</f>
+        <v>0.24869999999999998</v>
+      </c>
+      <c r="C359" s="7">
+        <f t="shared" ref="C359" si="350">C$246+H359</f>
+        <v>0.2084</v>
+      </c>
+      <c r="D359" s="7">
+        <f t="shared" ref="D359" si="351">D$246+I359</f>
+        <v>0.15760000000000002</v>
+      </c>
+      <c r="E359" s="4">
+        <f t="shared" ref="E359" si="352">E$246+J359</f>
+        <v>7.51E-2</v>
+      </c>
+      <c r="G359" s="10">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="H359" s="10">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="I359" s="10">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="J359" s="10">
+        <v>7.51E-2</v>
+      </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E360" s="9"/>
+      <c r="A360" s="3">
+        <v>46196</v>
+      </c>
+      <c r="B360" s="4">
+        <f t="shared" ref="B360" si="353">B$246+G360</f>
+        <v>0.24759999999999999</v>
+      </c>
+      <c r="C360" s="7">
+        <f t="shared" ref="C360" si="354">C$246+H360</f>
+        <v>0.2087</v>
+      </c>
+      <c r="D360" s="7">
+        <f t="shared" ref="D360" si="355">D$246+I360</f>
+        <v>0.1583</v>
+      </c>
+      <c r="E360" s="4">
+        <f t="shared" ref="E360" si="356">E$246+J360</f>
+        <v>6.2899999999999998E-2</v>
+      </c>
+      <c r="G360" s="10">
+        <v>7.7700000000000005E-2</v>
+      </c>
+      <c r="H360" s="10">
+        <v>9.2799999999999994E-2</v>
+      </c>
+      <c r="I360" s="10">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="J360" s="10">
+        <v>6.2899999999999998E-2</v>
+      </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E361" s="9"/>
+      <c r="A361" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B361" s="4">
+        <f t="shared" ref="B361" si="357">B$246+G361</f>
+        <v>0.24280000000000002</v>
+      </c>
+      <c r="C361" s="7">
+        <f t="shared" ref="C361" si="358">C$246+H361</f>
+        <v>0.1966</v>
+      </c>
+      <c r="D361" s="7">
+        <f t="shared" ref="D361" si="359">D$246+I361</f>
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="E361" s="4">
+        <f t="shared" ref="E361" si="360">E$246+J361</f>
+        <v>6.2E-2</v>
+      </c>
+      <c r="G361" s="10">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="H361" s="10">
+        <v>8.0699999999999994E-2</v>
+      </c>
+      <c r="I361" s="10">
+        <v>2.06E-2</v>
+      </c>
+      <c r="J361" s="10">
+        <v>6.2E-2</v>
+      </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E362" s="9"/>
+      <c r="A362" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B362" s="4">
+        <f t="shared" ref="B362" si="361">B$246+G362</f>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="C362" s="7">
+        <f t="shared" ref="C362" si="362">C$246+H362</f>
+        <v>0.19469999999999998</v>
+      </c>
+      <c r="D362" s="7">
+        <f t="shared" ref="D362" si="363">D$246+I362</f>
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="E362" s="4">
+        <f t="shared" ref="E362" si="364">E$246+J362</f>
+        <v>6.8099999999999994E-2</v>
+      </c>
+      <c r="G362" s="10">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="H362" s="10">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="I362" s="10">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="J362" s="10">
+        <v>6.8099999999999994E-2</v>
+      </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E363" s="9"/>
+      <c r="A363" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B363" s="4">
+        <f t="shared" ref="B363" si="365">B$246+G363</f>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="C363" s="7">
+        <f t="shared" ref="C363" si="366">C$246+H363</f>
+        <v>0.1971</v>
+      </c>
+      <c r="D363" s="7">
+        <f t="shared" ref="D363" si="367">D$246+I363</f>
+        <v>0.14549999999999999</v>
+      </c>
+      <c r="E363" s="4">
+        <f t="shared" ref="E363" si="368">E$246+J363</f>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="G363" s="10">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="H363" s="10">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="I363" s="10">
+        <v>2.58E-2</v>
+      </c>
+      <c r="J363" s="10">
+        <v>6.8500000000000005E-2</v>
+      </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E364" s="9"/>
+      <c r="A364" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B364" s="4">
+        <f t="shared" ref="B364" si="369">B$246+G364</f>
+        <v>0.2422</v>
+      </c>
+      <c r="C364" s="7">
+        <f t="shared" ref="C364" si="370">C$246+H364</f>
+        <v>0.1971</v>
+      </c>
+      <c r="D364" s="7">
+        <f t="shared" ref="D364" si="371">D$246+I364</f>
+        <v>0.1399</v>
+      </c>
+      <c r="E364" s="4">
+        <f t="shared" ref="E364" si="372">E$246+J364</f>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="G364" s="10">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="H364" s="10">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="I364" s="10">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="J364" s="10">
+        <v>6.8500000000000005E-2</v>
+      </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E365" s="9"/>
+      <c r="A365" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B365" s="4">
+        <f t="shared" ref="B365" si="373">B$246+G365</f>
+        <v>0.24230000000000002</v>
+      </c>
+      <c r="C365" s="7">
+        <f t="shared" ref="C365" si="374">C$246+H365</f>
+        <v>0.1971</v>
+      </c>
+      <c r="D365" s="7">
+        <f t="shared" ref="D365" si="375">D$246+I365</f>
+        <v>0.14629999999999999</v>
+      </c>
+      <c r="E365" s="4">
+        <f t="shared" ref="E365" si="376">E$246+J365</f>
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="G365" s="10">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="H365" s="10">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="I365" s="10">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="J365" s="10">
+        <v>6.8599999999999994E-2</v>
+      </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E366" s="9"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20220998-5FBA-4CD0-8259-3A1971D89802}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC2583A-27CC-4AF6-93B4-E7013CB61CBF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -44,6 +44,14 @@
   </si>
   <si>
     <t>EMP4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2호 증액 보정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4호 증액 보정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -160,7 +168,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -551,7 +558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S372"/>
+  <dimension ref="A1:S381"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -4762,16 +4769,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G247" s="10">
+      <c r="G247" s="9">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="H247" s="10">
-        <v>0</v>
-      </c>
-      <c r="I247" s="10">
-        <v>0</v>
-      </c>
-      <c r="J247" s="10">
+      <c r="H247" s="9">
+        <v>0</v>
+      </c>
+      <c r="I247" s="9">
+        <v>0</v>
+      </c>
+      <c r="J247" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4795,16 +4802,16 @@
         <f t="shared" ref="E248:E270" si="4">E$246+J248</f>
         <v>0</v>
       </c>
-      <c r="G248" s="10">
+      <c r="G248" s="9">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="H248" s="10">
+      <c r="H248" s="9">
         <v>-1E-4</v>
       </c>
-      <c r="I248" s="10">
-        <v>0</v>
-      </c>
-      <c r="J248" s="10">
+      <c r="I248" s="9">
+        <v>0</v>
+      </c>
+      <c r="J248" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4828,16 +4835,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G249" s="10">
+      <c r="G249" s="9">
         <v>1.67E-2</v>
       </c>
-      <c r="H249" s="10">
+      <c r="H249" s="9">
         <v>5.3E-3</v>
       </c>
-      <c r="I249" s="10">
+      <c r="I249" s="9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="J249" s="10">
+      <c r="J249" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4861,16 +4868,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G250" s="10">
+      <c r="G250" s="9">
         <v>1.2200000000000001E-2</v>
       </c>
-      <c r="H250" s="10">
+      <c r="H250" s="9">
         <v>1.8E-3</v>
       </c>
-      <c r="I250" s="10">
+      <c r="I250" s="9">
         <v>-1.4E-3</v>
       </c>
-      <c r="J250" s="10">
+      <c r="J250" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4894,16 +4901,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G251" s="10">
+      <c r="G251" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="H251" s="10">
+      <c r="H251" s="9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="I251" s="10">
+      <c r="I251" s="9">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="J251" s="10">
+      <c r="J251" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4927,16 +4934,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G252" s="10">
+      <c r="G252" s="9">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="H252" s="10">
+      <c r="H252" s="9">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="I252" s="10">
+      <c r="I252" s="9">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="J252" s="10">
+      <c r="J252" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4960,16 +4967,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G253" s="10">
+      <c r="G253" s="9">
         <v>2.58E-2</v>
       </c>
-      <c r="H253" s="10">
+      <c r="H253" s="9">
         <v>1.12E-2</v>
       </c>
-      <c r="I253" s="10">
+      <c r="I253" s="9">
         <v>6.3E-3</v>
       </c>
-      <c r="J253" s="10">
+      <c r="J253" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4993,16 +5000,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G254" s="10">
+      <c r="G254" s="9">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H254" s="10">
+      <c r="H254" s="9">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="I254" s="10">
+      <c r="I254" s="9">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="J254" s="10">
+      <c r="J254" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5026,16 +5033,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G255" s="10">
+      <c r="G255" s="9">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="H255" s="10">
+      <c r="H255" s="9">
         <v>1.03E-2</v>
       </c>
-      <c r="I255" s="10">
+      <c r="I255" s="9">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="J255" s="10">
+      <c r="J255" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5059,16 +5066,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G256" s="10">
+      <c r="G256" s="9">
         <v>2.64E-2</v>
       </c>
-      <c r="H256" s="10">
+      <c r="H256" s="9">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="I256" s="10">
+      <c r="I256" s="9">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="J256" s="10">
+      <c r="J256" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5092,16 +5099,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G257" s="10">
+      <c r="G257" s="9">
         <v>2.46E-2</v>
       </c>
-      <c r="H257" s="10">
+      <c r="H257" s="9">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="I257" s="10">
+      <c r="I257" s="9">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="J257" s="10">
+      <c r="J257" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5125,16 +5132,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G258" s="10">
+      <c r="G258" s="9">
         <v>2.46E-2</v>
       </c>
-      <c r="H258" s="10">
+      <c r="H258" s="9">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="I258" s="10">
+      <c r="I258" s="9">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="J258" s="10">
+      <c r="J258" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5158,16 +5165,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G259" s="10">
+      <c r="G259" s="9">
         <v>1.95E-2</v>
       </c>
-      <c r="H259" s="10">
+      <c r="H259" s="9">
         <v>2.8E-3</v>
       </c>
-      <c r="I259" s="10">
+      <c r="I259" s="9">
         <v>-7.3000000000000001E-3</v>
       </c>
-      <c r="J259" s="10">
+      <c r="J259" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5191,16 +5198,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G260" s="10">
+      <c r="G260" s="9">
         <v>3.04E-2</v>
       </c>
-      <c r="H260" s="10">
+      <c r="H260" s="9">
         <v>1.35E-2</v>
       </c>
-      <c r="I260" s="10">
+      <c r="I260" s="9">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="J260" s="10">
+      <c r="J260" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5224,16 +5231,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G261" s="10">
+      <c r="G261" s="9">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="H261" s="10">
+      <c r="H261" s="9">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="I261" s="10">
+      <c r="I261" s="9">
         <v>5.3E-3</v>
       </c>
-      <c r="J261" s="10">
+      <c r="J261" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5257,16 +5264,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G262" s="10">
+      <c r="G262" s="9">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="H262" s="10">
+      <c r="H262" s="9">
         <v>1.95E-2</v>
       </c>
-      <c r="I262" s="10">
+      <c r="I262" s="9">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="J262" s="10">
+      <c r="J262" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5290,16 +5297,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G263" s="10">
+      <c r="G263" s="9">
         <v>4.5100000000000001E-2</v>
       </c>
-      <c r="H263" s="10">
+      <c r="H263" s="9">
         <v>2.3099999999999999E-2</v>
       </c>
-      <c r="I263" s="10">
+      <c r="I263" s="9">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="J263" s="10">
+      <c r="J263" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5323,16 +5330,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G264" s="10">
+      <c r="G264" s="9">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="H264" s="10">
+      <c r="H264" s="9">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="I264" s="10">
+      <c r="I264" s="9">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="J264" s="10">
+      <c r="J264" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5356,16 +5363,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G265" s="10">
+      <c r="G265" s="9">
         <v>5.96E-2</v>
       </c>
-      <c r="H265" s="10">
+      <c r="H265" s="9">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="I265" s="10">
+      <c r="I265" s="9">
         <v>1.35E-2</v>
       </c>
-      <c r="J265" s="10">
+      <c r="J265" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5389,16 +5396,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G266" s="10">
+      <c r="G266" s="9">
         <v>0.06</v>
       </c>
-      <c r="H266" s="10">
+      <c r="H266" s="9">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="I266" s="10">
+      <c r="I266" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="J266" s="10">
+      <c r="J266" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5422,16 +5429,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G267" s="10">
+      <c r="G267" s="9">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="H267" s="10">
+      <c r="H267" s="9">
         <v>2.12E-2</v>
       </c>
-      <c r="I267" s="10">
+      <c r="I267" s="9">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="J267" s="10">
+      <c r="J267" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5455,16 +5462,16 @@
         <f t="shared" si="4"/>
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="G268" s="10">
+      <c r="G268" s="9">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H268" s="10">
+      <c r="H268" s="9">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="I268" s="10">
+      <c r="I268" s="9">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="J268" s="10">
+      <c r="J268" s="9">
         <v>-4.0000000000000002E-4</v>
       </c>
     </row>
@@ -5488,16 +5495,16 @@
         <f t="shared" si="4"/>
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="G269" s="10">
+      <c r="G269" s="9">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="H269" s="10">
+      <c r="H269" s="9">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="I269" s="10">
+      <c r="I269" s="9">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="J269" s="10">
+      <c r="J269" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
@@ -5521,16 +5528,16 @@
         <f t="shared" si="4"/>
         <v>-9.1999999999999998E-3</v>
       </c>
-      <c r="G270" s="10">
+      <c r="G270" s="9">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="H270" s="10">
+      <c r="H270" s="9">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="I270" s="10">
+      <c r="I270" s="9">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="J270" s="10">
+      <c r="J270" s="9">
         <v>-9.1999999999999998E-3</v>
       </c>
     </row>
@@ -5554,16 +5561,16 @@
         <f t="shared" ref="E271" si="7">E$246+J271</f>
         <v>-1.5600000000000001E-2</v>
       </c>
-      <c r="G271" s="10">
+      <c r="G271" s="9">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="H271" s="10">
+      <c r="H271" s="9">
         <v>1.26E-2</v>
       </c>
-      <c r="I271" s="10">
+      <c r="I271" s="9">
         <v>-1.6000000000000001E-3</v>
       </c>
-      <c r="J271" s="10">
+      <c r="J271" s="9">
         <v>-1.5600000000000001E-2</v>
       </c>
     </row>
@@ -5587,16 +5594,16 @@
         <f t="shared" ref="E272" si="11">E$246+J272</f>
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="G272" s="10">
+      <c r="G272" s="9">
         <v>4.1500000000000002E-2</v>
       </c>
-      <c r="H272" s="10">
+      <c r="H272" s="9">
         <v>2.87E-2</v>
       </c>
-      <c r="I272" s="10">
+      <c r="I272" s="9">
         <v>1.34E-2</v>
       </c>
-      <c r="J272" s="10">
+      <c r="J272" s="9">
         <v>-4.7000000000000002E-3</v>
       </c>
     </row>
@@ -5620,16 +5627,16 @@
         <f t="shared" si="12"/>
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="G273" s="10">
+      <c r="G273" s="9">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H273" s="10">
+      <c r="H273" s="9">
         <v>3.49E-2</v>
       </c>
-      <c r="I273" s="10">
+      <c r="I273" s="9">
         <v>1.89E-2</v>
       </c>
-      <c r="J273" s="10">
+      <c r="J273" s="9">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
@@ -5653,16 +5660,16 @@
         <f t="shared" si="12"/>
         <v>-2.8E-3</v>
       </c>
-      <c r="G274" s="10">
+      <c r="G274" s="9">
         <v>4.8500000000000001E-2</v>
       </c>
-      <c r="H274" s="10">
+      <c r="H274" s="9">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="I274" s="10">
+      <c r="I274" s="9">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="J274" s="10">
+      <c r="J274" s="9">
         <v>-2.8E-3</v>
       </c>
     </row>
@@ -5686,16 +5693,16 @@
         <f t="shared" ref="E275" si="16">E$246+J275</f>
         <v>-5.4000000000000003E-3</v>
       </c>
-      <c r="G275" s="10">
+      <c r="G275" s="9">
         <v>5.1700000000000003E-2</v>
       </c>
-      <c r="H275" s="10">
+      <c r="H275" s="9">
         <v>3.8100000000000002E-2</v>
       </c>
-      <c r="I275" s="10">
+      <c r="I275" s="9">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="J275" s="10">
+      <c r="J275" s="9">
         <v>-5.4000000000000003E-3</v>
       </c>
     </row>
@@ -5719,16 +5726,16 @@
         <f t="shared" ref="E276" si="20">E$246+J276</f>
         <v>-1.7500000000000002E-2</v>
       </c>
-      <c r="G276" s="10">
+      <c r="G276" s="9">
         <v>3.95E-2</v>
       </c>
-      <c r="H276" s="10">
+      <c r="H276" s="9">
         <v>2.8199999999999999E-2</v>
       </c>
-      <c r="I276" s="10">
+      <c r="I276" s="9">
         <v>1.24E-2</v>
       </c>
-      <c r="J276" s="10">
+      <c r="J276" s="9">
         <v>-1.7500000000000002E-2</v>
       </c>
     </row>
@@ -5752,16 +5759,16 @@
         <f t="shared" ref="E277" si="24">E$246+J277</f>
         <v>-7.1999999999999998E-3</v>
       </c>
-      <c r="G277" s="10">
+      <c r="G277" s="9">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="H277" s="10">
+      <c r="H277" s="9">
         <v>3.3599999999999998E-2</v>
       </c>
-      <c r="I277" s="10">
+      <c r="I277" s="9">
         <v>1.77E-2</v>
       </c>
-      <c r="J277" s="10">
+      <c r="J277" s="9">
         <v>-7.1999999999999998E-3</v>
       </c>
     </row>
@@ -5785,16 +5792,16 @@
         <f t="shared" ref="E278" si="28">E$246+J278</f>
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="G278" s="10">
+      <c r="G278" s="9">
         <v>4.65E-2</v>
       </c>
-      <c r="H278" s="10">
+      <c r="H278" s="9">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="I278" s="10">
+      <c r="I278" s="9">
         <v>1.67E-2</v>
       </c>
-      <c r="J278" s="10">
+      <c r="J278" s="9">
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
@@ -5818,16 +5825,16 @@
         <f t="shared" ref="E279" si="32">E$246+J279</f>
         <v>-1.01E-2</v>
       </c>
-      <c r="G279" s="10">
+      <c r="G279" s="9">
         <v>5.3900000000000003E-2</v>
       </c>
-      <c r="H279" s="10">
+      <c r="H279" s="9">
         <v>4.3299999999999998E-2</v>
       </c>
-      <c r="I279" s="10">
+      <c r="I279" s="9">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="J279" s="10">
+      <c r="J279" s="9">
         <v>-1.01E-2</v>
       </c>
     </row>
@@ -5851,16 +5858,16 @@
         <f t="shared" ref="E280" si="36">E$246+J280</f>
         <v>-9.9000000000000008E-3</v>
       </c>
-      <c r="G280" s="10">
+      <c r="G280" s="9">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="H280" s="10">
+      <c r="H280" s="9">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="I280" s="10">
+      <c r="I280" s="9">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="J280" s="10">
+      <c r="J280" s="9">
         <v>-9.9000000000000008E-3</v>
       </c>
     </row>
@@ -5884,16 +5891,16 @@
         <f t="shared" ref="E281" si="40">E$246+J281</f>
         <v>-1.1299999999999999E-2</v>
       </c>
-      <c r="G281" s="10">
+      <c r="G281" s="9">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="H281" s="10">
+      <c r="H281" s="9">
         <v>4.48E-2</v>
       </c>
-      <c r="I281" s="10">
+      <c r="I281" s="9">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="J281" s="10">
+      <c r="J281" s="9">
         <v>-1.1299999999999999E-2</v>
       </c>
     </row>
@@ -5917,16 +5924,16 @@
         <f t="shared" ref="E282" si="44">E$246+J282</f>
         <v>-1.2E-2</v>
       </c>
-      <c r="G282" s="10">
+      <c r="G282" s="9">
         <v>5.9900000000000002E-2</v>
       </c>
-      <c r="H282" s="10">
+      <c r="H282" s="9">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="I282" s="10">
+      <c r="I282" s="9">
         <v>2.7E-2</v>
       </c>
-      <c r="J282" s="10">
+      <c r="J282" s="9">
         <v>-1.2E-2</v>
       </c>
     </row>
@@ -5950,16 +5957,16 @@
         <f t="shared" ref="E283" si="48">E$246+J283</f>
         <v>-1.3899999999999999E-2</v>
       </c>
-      <c r="G283" s="10">
+      <c r="G283" s="9">
         <v>5.8299999999999998E-2</v>
       </c>
-      <c r="H283" s="10">
+      <c r="H283" s="9">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="I283" s="10">
+      <c r="I283" s="9">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="J283" s="10">
+      <c r="J283" s="9">
         <v>-1.3899999999999999E-2</v>
       </c>
     </row>
@@ -5983,16 +5990,16 @@
         <f t="shared" ref="E284" si="52">E$246+J284</f>
         <v>-1.52E-2</v>
       </c>
-      <c r="G284" s="10">
+      <c r="G284" s="9">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="H284" s="10">
+      <c r="H284" s="9">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="I284" s="10">
+      <c r="I284" s="9">
         <v>0.02</v>
       </c>
-      <c r="J284" s="10">
+      <c r="J284" s="9">
         <v>-1.52E-2</v>
       </c>
     </row>
@@ -6016,16 +6023,16 @@
         <f t="shared" ref="E285" si="56">E$246+J285</f>
         <v>-2.2800000000000001E-2</v>
       </c>
-      <c r="G285" s="10">
+      <c r="G285" s="9">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="H285" s="10">
+      <c r="H285" s="9">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="I285" s="10">
+      <c r="I285" s="9">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="J285" s="10">
+      <c r="J285" s="9">
         <v>-2.2800000000000001E-2</v>
       </c>
     </row>
@@ -6049,16 +6056,16 @@
         <f t="shared" ref="E286" si="60">E$246+J286</f>
         <v>-1.44E-2</v>
       </c>
-      <c r="G286" s="10">
+      <c r="G286" s="9">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="H286" s="10">
+      <c r="H286" s="9">
         <v>3.3599999999999998E-2</v>
       </c>
-      <c r="I286" s="10">
+      <c r="I286" s="9">
         <v>1.32E-2</v>
       </c>
-      <c r="J286" s="10">
+      <c r="J286" s="9">
         <v>-1.44E-2</v>
       </c>
     </row>
@@ -6082,16 +6089,16 @@
         <f t="shared" ref="E287" si="64">E$246+J287</f>
         <v>-4.7000000000000002E-3</v>
       </c>
-      <c r="G287" s="10">
+      <c r="G287" s="9">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="H287" s="10">
+      <c r="H287" s="9">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="I287" s="10">
+      <c r="I287" s="9">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="J287" s="10">
+      <c r="J287" s="9">
         <v>-4.7000000000000002E-3</v>
       </c>
     </row>
@@ -6115,16 +6122,16 @@
         <f t="shared" ref="E288" si="68">E$246+J288</f>
         <v>-9.5999999999999992E-3</v>
       </c>
-      <c r="G288" s="10">
+      <c r="G288" s="9">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="H288" s="10">
+      <c r="H288" s="9">
         <v>1.89E-2</v>
       </c>
-      <c r="I288" s="10">
+      <c r="I288" s="9">
         <v>-1E-4</v>
       </c>
-      <c r="J288" s="10">
+      <c r="J288" s="9">
         <v>-9.5999999999999992E-3</v>
       </c>
     </row>
@@ -6148,16 +6155,16 @@
         <f t="shared" ref="E289" si="72">E$246+J289</f>
         <v>-1.6E-2</v>
       </c>
-      <c r="G289" s="10">
+      <c r="G289" s="9">
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="H289" s="10">
+      <c r="H289" s="9">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I289" s="10">
+      <c r="I289" s="9">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="J289" s="10">
+      <c r="J289" s="9">
         <v>-1.6E-2</v>
       </c>
     </row>
@@ -6181,16 +6188,16 @@
         <f t="shared" ref="E290" si="76">E$246+J290</f>
         <v>-1.8200000000000001E-2</v>
       </c>
-      <c r="G290" s="10">
+      <c r="G290" s="9">
         <v>4.4900000000000002E-2</v>
       </c>
-      <c r="H290" s="10">
+      <c r="H290" s="9">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="I290" s="10">
+      <c r="I290" s="9">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="J290" s="10">
+      <c r="J290" s="9">
         <v>-1.8200000000000001E-2</v>
       </c>
     </row>
@@ -6214,16 +6221,16 @@
         <f t="shared" ref="E291" si="80">E$246+J291</f>
         <v>-1.6E-2</v>
       </c>
-      <c r="G291" s="10">
+      <c r="G291" s="9">
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="H291" s="10">
+      <c r="H291" s="9">
         <v>1.89E-2</v>
       </c>
-      <c r="I291" s="10">
+      <c r="I291" s="9">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J291" s="10">
+      <c r="J291" s="9">
         <v>-1.6E-2</v>
       </c>
     </row>
@@ -6247,16 +6254,16 @@
         <f t="shared" ref="E292" si="84">E$246+J292</f>
         <v>-1.5299999999999999E-2</v>
       </c>
-      <c r="G292" s="10">
+      <c r="G292" s="9">
         <v>3.9100000000000003E-2</v>
       </c>
-      <c r="H292" s="10">
+      <c r="H292" s="9">
         <v>1.01E-2</v>
       </c>
-      <c r="I292" s="10">
+      <c r="I292" s="9">
         <v>-1.5E-3</v>
       </c>
-      <c r="J292" s="10">
+      <c r="J292" s="9">
         <v>-1.5299999999999999E-2</v>
       </c>
     </row>
@@ -6280,16 +6287,16 @@
         <f t="shared" ref="E293" si="88">E$246+J293</f>
         <v>-1.34E-2</v>
       </c>
-      <c r="G293" s="10">
+      <c r="G293" s="9">
         <v>3.6400000000000002E-2</v>
       </c>
-      <c r="H293" s="10">
+      <c r="H293" s="9">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="I293" s="10">
+      <c r="I293" s="9">
         <v>-3.3999999999999998E-3</v>
       </c>
-      <c r="J293" s="10">
+      <c r="J293" s="9">
         <v>-1.34E-2</v>
       </c>
     </row>
@@ -6313,16 +6320,16 @@
         <f t="shared" ref="E294" si="92">E$246+J294</f>
         <v>-1.43E-2</v>
       </c>
-      <c r="G294" s="10">
+      <c r="G294" s="9">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="H294" s="10">
+      <c r="H294" s="9">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I294" s="10">
+      <c r="I294" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="J294" s="10">
+      <c r="J294" s="9">
         <v>-1.43E-2</v>
       </c>
     </row>
@@ -6346,16 +6353,16 @@
         <f t="shared" ref="E295" si="96">E$246+J295</f>
         <v>-1.37E-2</v>
       </c>
-      <c r="G295" s="10">
+      <c r="G295" s="9">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="H295" s="10">
+      <c r="H295" s="9">
         <v>1.35E-2</v>
       </c>
-      <c r="I295" s="10">
+      <c r="I295" s="9">
         <v>2.3E-3</v>
       </c>
-      <c r="J295" s="10">
+      <c r="J295" s="9">
         <v>-1.37E-2</v>
       </c>
     </row>
@@ -6379,16 +6386,16 @@
         <f t="shared" ref="E296" si="100">E$246+J296</f>
         <v>-1.6500000000000001E-2</v>
       </c>
-      <c r="G296" s="10">
+      <c r="G296" s="9">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="H296" s="10">
+      <c r="H296" s="9">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="I296" s="10">
+      <c r="I296" s="9">
         <v>-2.2000000000000001E-3</v>
       </c>
-      <c r="J296" s="10">
+      <c r="J296" s="9">
         <v>-1.6500000000000001E-2</v>
       </c>
     </row>
@@ -6412,16 +6419,16 @@
         <f t="shared" ref="E297" si="104">E$246+J297</f>
         <v>-1.8200000000000001E-2</v>
       </c>
-      <c r="G297" s="10">
+      <c r="G297" s="9">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="H297" s="10">
+      <c r="H297" s="9">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="I297" s="10">
+      <c r="I297" s="9">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="J297" s="10">
+      <c r="J297" s="9">
         <v>-1.8200000000000001E-2</v>
       </c>
     </row>
@@ -6445,16 +6452,16 @@
         <f t="shared" ref="E298" si="108">E$246+J298</f>
         <v>-2.06E-2</v>
       </c>
-      <c r="G298" s="10">
+      <c r="G298" s="9">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="H298" s="10">
+      <c r="H298" s="9">
         <v>-2.7000000000000001E-3</v>
       </c>
-      <c r="I298" s="10">
+      <c r="I298" s="9">
         <v>-1.0200000000000001E-2</v>
       </c>
-      <c r="J298" s="10">
+      <c r="J298" s="9">
         <v>-2.06E-2</v>
       </c>
     </row>
@@ -6478,16 +6485,16 @@
         <f t="shared" ref="E299" si="112">E$246+J299</f>
         <v>-2.23E-2</v>
       </c>
-      <c r="G299" s="10">
+      <c r="G299" s="9">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="H299" s="10">
+      <c r="H299" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I299" s="10">
+      <c r="I299" s="9">
         <v>-6.4000000000000003E-3</v>
       </c>
-      <c r="J299" s="10">
+      <c r="J299" s="9">
         <v>-2.23E-2</v>
       </c>
     </row>
@@ -6511,16 +6518,16 @@
         <f t="shared" ref="E300" si="116">E$246+J300</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G300" s="10">
+      <c r="G300" s="9">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="H300" s="10">
+      <c r="H300" s="9">
         <v>-1.9E-3</v>
       </c>
-      <c r="I300" s="10">
+      <c r="I300" s="9">
         <v>-7.4999999999999997E-3</v>
       </c>
-      <c r="J300" s="10">
+      <c r="J300" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6544,16 +6551,16 @@
         <f t="shared" ref="E301" si="120">E$246+J301</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G301" s="10">
+      <c r="G301" s="9">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="H301" s="10">
+      <c r="H301" s="9">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="I301" s="10">
+      <c r="I301" s="9">
         <v>-4.5999999999999999E-3</v>
       </c>
-      <c r="J301" s="10">
+      <c r="J301" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6577,16 +6584,16 @@
         <f t="shared" ref="E302" si="124">E$246+J302</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G302" s="10">
+      <c r="G302" s="9">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="H302" s="10">
+      <c r="H302" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I302" s="10">
+      <c r="I302" s="9">
         <v>-1.09E-2</v>
       </c>
-      <c r="J302" s="10">
+      <c r="J302" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6610,16 +6617,16 @@
         <f t="shared" ref="E303" si="128">E$246+J303</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G303" s="10">
+      <c r="G303" s="9">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="H303" s="10">
+      <c r="H303" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I303" s="10">
+      <c r="I303" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J303" s="10">
+      <c r="J303" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6643,16 +6650,16 @@
         <f t="shared" ref="E304" si="132">E$246+J304</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G304" s="10">
+      <c r="G304" s="9">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="H304" s="10">
+      <c r="H304" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I304" s="10">
+      <c r="I304" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J304" s="10">
+      <c r="J304" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6676,16 +6683,16 @@
         <f t="shared" ref="E305" si="136">E$246+J305</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G305" s="10">
+      <c r="G305" s="9">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="H305" s="10">
+      <c r="H305" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I305" s="10">
+      <c r="I305" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J305" s="10">
+      <c r="J305" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6709,16 +6716,16 @@
         <f t="shared" ref="E306" si="140">E$246+J306</f>
         <v>-2.1899999999999999E-2</v>
       </c>
-      <c r="G306" s="10">
+      <c r="G306" s="9">
         <v>2.47E-2</v>
       </c>
-      <c r="H306" s="10">
+      <c r="H306" s="9">
         <v>-5.1000000000000004E-3</v>
       </c>
-      <c r="I306" s="10">
+      <c r="I306" s="9">
         <v>-1.34E-2</v>
       </c>
-      <c r="J306" s="10">
+      <c r="J306" s="9">
         <v>-2.1899999999999999E-2</v>
       </c>
     </row>
@@ -6742,16 +6749,16 @@
         <f t="shared" ref="E307" si="144">E$246+J307</f>
         <v>-2.24E-2</v>
       </c>
-      <c r="G307" s="10">
+      <c r="G307" s="9">
         <v>3.1E-2</v>
       </c>
-      <c r="H307" s="10">
+      <c r="H307" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I307" s="10">
+      <c r="I307" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J307" s="10">
+      <c r="J307" s="9">
         <v>-2.24E-2</v>
       </c>
     </row>
@@ -6775,16 +6782,16 @@
         <f t="shared" ref="E308" si="148">E$246+J308</f>
         <v>-2.2599999999999999E-2</v>
       </c>
-      <c r="G308" s="10">
+      <c r="G308" s="9">
         <v>3.1E-2</v>
       </c>
-      <c r="H308" s="10">
+      <c r="H308" s="9">
         <v>-4.1999999999999997E-3</v>
       </c>
-      <c r="I308" s="10">
+      <c r="I308" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J308" s="10">
+      <c r="J308" s="9">
         <v>-2.2599999999999999E-2</v>
       </c>
     </row>
@@ -6808,16 +6815,16 @@
         <f t="shared" ref="E309" si="152">E$246+J309</f>
         <v>-2.3300000000000001E-2</v>
       </c>
-      <c r="G309" s="10">
+      <c r="G309" s="9">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="H309" s="10">
+      <c r="H309" s="9">
         <v>-4.1000000000000003E-3</v>
       </c>
-      <c r="I309" s="10">
+      <c r="I309" s="9">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="J309" s="10">
+      <c r="J309" s="9">
         <v>-2.3300000000000001E-2</v>
       </c>
     </row>
@@ -6841,16 +6848,16 @@
         <f t="shared" ref="E310" si="156">E$246+J310</f>
         <v>-0.01</v>
       </c>
-      <c r="G310" s="10">
+      <c r="G310" s="9">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="H310" s="10">
+      <c r="H310" s="9">
         <v>-1.6999999999999999E-3</v>
       </c>
-      <c r="I310" s="10">
+      <c r="I310" s="9">
         <v>-1.11E-2</v>
       </c>
-      <c r="J310" s="10">
+      <c r="J310" s="9">
         <v>-0.01</v>
       </c>
     </row>
@@ -6874,16 +6881,16 @@
         <f t="shared" ref="E311" si="160">E$246+J311</f>
         <v>-1.06E-2</v>
       </c>
-      <c r="G311" s="10">
+      <c r="G311" s="9">
         <v>4.53E-2</v>
       </c>
-      <c r="H311" s="10">
+      <c r="H311" s="9">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="I311" s="10">
+      <c r="I311" s="9">
         <v>-3.0999999999999999E-3</v>
       </c>
-      <c r="J311" s="10">
+      <c r="J311" s="9">
         <v>-1.06E-2</v>
       </c>
     </row>
@@ -6907,16 +6914,16 @@
         <f t="shared" ref="E312" si="164">E$246+J312</f>
         <v>-1.6000000000000001E-3</v>
       </c>
-      <c r="G312" s="10">
+      <c r="G312" s="9">
         <v>4.8399999999999999E-2</v>
       </c>
-      <c r="H312" s="10">
+      <c r="H312" s="9">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="I312" s="10">
+      <c r="I312" s="9">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="J312" s="10">
+      <c r="J312" s="9">
         <v>-1.6000000000000001E-3</v>
       </c>
     </row>
@@ -6940,16 +6947,16 @@
         <f t="shared" ref="E313" si="168">E$246+J313</f>
         <v>-3.3E-3</v>
       </c>
-      <c r="G313" s="10">
+      <c r="G313" s="9">
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="H313" s="10">
+      <c r="H313" s="9">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="I313" s="10">
+      <c r="I313" s="9">
         <v>-3.2000000000000002E-3</v>
       </c>
-      <c r="J313" s="10">
+      <c r="J313" s="9">
         <v>-3.3E-3</v>
       </c>
     </row>
@@ -6973,16 +6980,16 @@
         <f t="shared" ref="E314" si="172">E$246+J314</f>
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G314" s="10">
+      <c r="G314" s="9">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="H314" s="10">
+      <c r="H314" s="9">
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="I314" s="10">
+      <c r="I314" s="9">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="J314" s="10">
+      <c r="J314" s="9">
         <v>5.1999999999999998E-3</v>
       </c>
     </row>
@@ -7006,16 +7013,16 @@
         <f t="shared" ref="E315" si="176">E$246+J315</f>
         <v>1.11E-2</v>
       </c>
-      <c r="G315" s="10">
+      <c r="G315" s="9">
         <v>5.8599999999999999E-2</v>
       </c>
-      <c r="H315" s="10">
+      <c r="H315" s="9">
         <v>3.04E-2</v>
       </c>
-      <c r="I315" s="10">
+      <c r="I315" s="9">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="J315" s="10">
+      <c r="J315" s="9">
         <v>1.11E-2</v>
       </c>
     </row>
@@ -7039,16 +7046,16 @@
         <f t="shared" ref="E316" si="180">E$246+J316</f>
         <v>1.4E-2</v>
       </c>
-      <c r="G316" s="10">
+      <c r="G316" s="9">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="H316" s="10">
+      <c r="H316" s="9">
         <v>3.1E-2</v>
       </c>
-      <c r="I316" s="10">
+      <c r="I316" s="9">
         <v>5.3E-3</v>
       </c>
-      <c r="J316" s="10">
+      <c r="J316" s="9">
         <v>1.4E-2</v>
       </c>
     </row>
@@ -7072,16 +7079,16 @@
         <f t="shared" ref="E317" si="184">E$246+J317</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G317" s="10">
+      <c r="G317" s="9">
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="H317" s="10">
+      <c r="H317" s="9">
         <v>3.4299999999999997E-2</v>
       </c>
-      <c r="I317" s="10">
+      <c r="I317" s="9">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J317" s="10">
+      <c r="J317" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -7105,16 +7112,16 @@
         <f t="shared" ref="E318" si="188">E$246+J318</f>
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G318" s="10">
+      <c r="G318" s="9">
         <v>6.6799999999999998E-2</v>
       </c>
-      <c r="H318" s="10">
+      <c r="H318" s="9">
         <v>4.3799999999999999E-2</v>
       </c>
-      <c r="I318" s="10">
+      <c r="I318" s="9">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="J318" s="10">
+      <c r="J318" s="9">
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
@@ -7138,16 +7145,16 @@
         <f t="shared" ref="E319" si="192">E$246+J319</f>
         <v>1.8599999999999998E-2</v>
       </c>
-      <c r="G319" s="10">
+      <c r="G319" s="9">
         <v>6.6199999999999995E-2</v>
       </c>
-      <c r="H319" s="10">
+      <c r="H319" s="9">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="I319" s="10">
+      <c r="I319" s="9">
         <v>1.01E-2</v>
       </c>
-      <c r="J319" s="10">
+      <c r="J319" s="9">
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
@@ -7171,16 +7178,16 @@
         <f t="shared" ref="E320" si="196">E$246+J320</f>
         <v>1.52E-2</v>
       </c>
-      <c r="G320" s="10">
+      <c r="G320" s="9">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="H320" s="10">
+      <c r="H320" s="9">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="I320" s="10">
+      <c r="I320" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J320" s="10">
+      <c r="J320" s="9">
         <v>1.52E-2</v>
       </c>
     </row>
@@ -7204,19 +7211,19 @@
         <f t="shared" ref="E321" si="200">E$246+J321</f>
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="G321" s="10">
+      <c r="G321" s="9">
         <v>6.54E-2</v>
       </c>
-      <c r="H321" s="10">
+      <c r="H321" s="9">
         <v>4.2200000000000001E-2</v>
       </c>
-      <c r="I321" s="10">
+      <c r="I321" s="9">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="J321" s="10">
+      <c r="J321" s="9">
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="S321" s="11"/>
+      <c r="S321" s="10"/>
     </row>
     <row r="322" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
@@ -7238,16 +7245,16 @@
         <f t="shared" ref="E322" si="204">E$246+J322</f>
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="G322" s="10">
+      <c r="G322" s="9">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="H322" s="10">
+      <c r="H322" s="9">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="I322" s="10">
+      <c r="I322" s="9">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="J322" s="10">
+      <c r="J322" s="9">
         <v>1.6899999999999998E-2</v>
       </c>
     </row>
@@ -7271,16 +7278,16 @@
         <f t="shared" ref="E323" si="208">E$246+J323</f>
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="G323" s="10">
+      <c r="G323" s="9">
         <v>6.7900000000000002E-2</v>
       </c>
-      <c r="H323" s="10">
+      <c r="H323" s="9">
         <v>4.3799999999999999E-2</v>
       </c>
-      <c r="I323" s="10">
+      <c r="I323" s="9">
         <v>1.24E-2</v>
       </c>
-      <c r="J323" s="10">
+      <c r="J323" s="9">
         <v>2.0899999999999998E-2</v>
       </c>
     </row>
@@ -7304,16 +7311,16 @@
         <f t="shared" ref="E324" si="212">E$246+J324</f>
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G324" s="10">
+      <c r="G324" s="9">
         <v>6.54E-2</v>
       </c>
-      <c r="H324" s="10">
+      <c r="H324" s="9">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="I324" s="10">
+      <c r="I324" s="9">
         <v>1.03E-2</v>
       </c>
-      <c r="J324" s="10">
+      <c r="J324" s="9">
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
@@ -7337,16 +7344,16 @@
         <f t="shared" ref="E325" si="216">E$246+J325</f>
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G325" s="10">
+      <c r="G325" s="9">
         <v>6.54E-2</v>
       </c>
-      <c r="H325" s="10">
+      <c r="H325" s="9">
         <v>3.7699999999999997E-2</v>
       </c>
-      <c r="I325" s="10">
+      <c r="I325" s="9">
         <v>1.03E-2</v>
       </c>
-      <c r="J325" s="10">
+      <c r="J325" s="9">
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
@@ -7370,16 +7377,16 @@
         <f t="shared" ref="E326" si="220">E$246+J326</f>
         <v>1.46E-2</v>
       </c>
-      <c r="G326" s="10">
+      <c r="G326" s="9">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="H326" s="10">
+      <c r="H326" s="9">
         <v>3.6400000000000002E-2</v>
       </c>
-      <c r="I326" s="10">
+      <c r="I326" s="9">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="J326" s="10">
+      <c r="J326" s="9">
         <v>1.46E-2</v>
       </c>
     </row>
@@ -7403,16 +7410,16 @@
         <f t="shared" ref="E327" si="224">E$246+J327</f>
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="G327" s="10">
+      <c r="G327" s="9">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="H327" s="10">
+      <c r="H327" s="9">
         <v>4.8399999999999999E-2</v>
       </c>
-      <c r="I327" s="10">
+      <c r="I327" s="9">
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="J327" s="10">
+      <c r="J327" s="9">
         <v>2.4899999999999999E-2</v>
       </c>
     </row>
@@ -7436,16 +7443,16 @@
         <f t="shared" ref="E328" si="228">E$246+J328</f>
         <v>3.49E-2</v>
       </c>
-      <c r="G328" s="10">
+      <c r="G328" s="9">
         <v>7.3899999999999993E-2</v>
       </c>
-      <c r="H328" s="10">
+      <c r="H328" s="9">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="I328" s="10">
+      <c r="I328" s="9">
         <v>2.53E-2</v>
       </c>
-      <c r="J328" s="10">
+      <c r="J328" s="9">
         <v>3.49E-2</v>
       </c>
     </row>
@@ -7469,16 +7476,16 @@
         <f t="shared" ref="E329" si="232">E$246+J329</f>
         <v>4.5900000000000003E-2</v>
       </c>
-      <c r="G329" s="10">
+      <c r="G329" s="9">
         <v>8.1100000000000005E-2</v>
       </c>
-      <c r="H329" s="10">
+      <c r="H329" s="9">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="I329" s="10">
+      <c r="I329" s="9">
         <v>3.5799999999999998E-2</v>
       </c>
-      <c r="J329" s="10">
+      <c r="J329" s="9">
         <v>4.5900000000000003E-2</v>
       </c>
     </row>
@@ -7502,16 +7509,16 @@
         <f t="shared" ref="E330" si="236">E$246+J330</f>
         <v>4.53E-2</v>
       </c>
-      <c r="G330" s="10">
+      <c r="G330" s="9">
         <v>7.7399999999999997E-2</v>
       </c>
-      <c r="H330" s="10">
+      <c r="H330" s="9">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="I330" s="10">
+      <c r="I330" s="9">
         <v>2.9100000000000001E-2</v>
       </c>
-      <c r="J330" s="10">
+      <c r="J330" s="9">
         <v>4.53E-2</v>
       </c>
     </row>
@@ -7535,16 +7542,16 @@
         <f t="shared" ref="E331" si="240">E$246+J331</f>
         <v>5.3400000000000003E-2</v>
       </c>
-      <c r="G331" s="10">
+      <c r="G331" s="9">
         <v>8.3199999999999996E-2</v>
       </c>
-      <c r="H331" s="10">
+      <c r="H331" s="9">
         <v>7.9399999999999998E-2</v>
       </c>
-      <c r="I331" s="10">
+      <c r="I331" s="9">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="J331" s="10">
+      <c r="J331" s="9">
         <v>5.3400000000000003E-2</v>
       </c>
     </row>
@@ -7568,16 +7575,16 @@
         <f t="shared" ref="E332" si="244">E$246+J332</f>
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="G332" s="10">
+      <c r="G332" s="9">
         <v>8.5400000000000004E-2</v>
       </c>
-      <c r="H332" s="10">
+      <c r="H332" s="9">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="I332" s="10">
+      <c r="I332" s="9">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="J332" s="10">
+      <c r="J332" s="9">
         <v>5.7700000000000001E-2</v>
       </c>
     </row>
@@ -7601,16 +7608,16 @@
         <f t="shared" ref="E333" si="248">E$246+J333</f>
         <v>6.4199999999999993E-2</v>
       </c>
-      <c r="G333" s="10">
+      <c r="G333" s="9">
         <v>8.4900000000000003E-2</v>
       </c>
-      <c r="H333" s="10">
+      <c r="H333" s="9">
         <v>7.5600000000000001E-2</v>
       </c>
-      <c r="I333" s="10">
+      <c r="I333" s="9">
         <v>3.49E-2</v>
       </c>
-      <c r="J333" s="10">
+      <c r="J333" s="9">
         <v>6.4199999999999993E-2</v>
       </c>
     </row>
@@ -7634,16 +7641,16 @@
         <f t="shared" ref="E334" si="252">E$246+J334</f>
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="G334" s="10">
+      <c r="G334" s="9">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="H334" s="10">
+      <c r="H334" s="9">
         <v>8.5099999999999995E-2</v>
       </c>
-      <c r="I334" s="10">
+      <c r="I334" s="9">
         <v>3.85E-2</v>
       </c>
-      <c r="J334" s="10">
+      <c r="J334" s="9">
         <v>6.6699999999999995E-2</v>
       </c>
     </row>
@@ -7667,16 +7674,16 @@
         <f t="shared" ref="E335" si="256">E$246+J335</f>
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="G335" s="10">
+      <c r="G335" s="9">
         <v>8.8499999999999995E-2</v>
       </c>
-      <c r="H335" s="10">
+      <c r="H335" s="9">
         <v>8.6499999999999994E-2</v>
       </c>
-      <c r="I335" s="10">
+      <c r="I335" s="9">
         <v>3.9800000000000002E-2</v>
       </c>
-      <c r="J335" s="10">
+      <c r="J335" s="9">
         <v>5.4899999999999997E-2</v>
       </c>
     </row>
@@ -7700,16 +7707,16 @@
         <f t="shared" ref="E336" si="260">E$246+J336</f>
         <v>4.7199999999999999E-2</v>
       </c>
-      <c r="G336" s="10">
+      <c r="G336" s="9">
         <v>7.7100000000000002E-2</v>
       </c>
-      <c r="H336" s="10">
+      <c r="H336" s="9">
         <v>7.0400000000000004E-2</v>
       </c>
-      <c r="I336" s="10">
+      <c r="I336" s="9">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J336" s="10">
+      <c r="J336" s="9">
         <v>4.7199999999999999E-2</v>
       </c>
     </row>
@@ -7733,16 +7740,16 @@
         <f t="shared" ref="E337" si="264">E$246+J337</f>
         <v>4.6300000000000001E-2</v>
       </c>
-      <c r="G337" s="10">
+      <c r="G337" s="9">
         <v>7.8200000000000006E-2</v>
       </c>
-      <c r="H337" s="10">
+      <c r="H337" s="9">
         <v>6.5500000000000003E-2</v>
       </c>
-      <c r="I337" s="10">
+      <c r="I337" s="9">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="J337" s="10">
+      <c r="J337" s="9">
         <v>4.6300000000000001E-2</v>
       </c>
     </row>
@@ -7766,16 +7773,16 @@
         <f t="shared" ref="E338" si="268">E$246+J338</f>
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="G338" s="10">
+      <c r="G338" s="9">
         <v>7.5300000000000006E-2</v>
       </c>
-      <c r="H338" s="10">
+      <c r="H338" s="9">
         <v>6.0199999999999997E-2</v>
       </c>
-      <c r="I338" s="10">
+      <c r="I338" s="9">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="J338" s="10">
+      <c r="J338" s="9">
         <v>4.1799999999999997E-2</v>
       </c>
     </row>
@@ -7799,16 +7806,16 @@
         <f t="shared" ref="E339" si="272">E$246+J339</f>
         <v>5.6300000000000003E-2</v>
       </c>
-      <c r="G339" s="10">
+      <c r="G339" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="H339" s="10">
+      <c r="H339" s="9">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="I339" s="10">
+      <c r="I339" s="9">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="J339" s="10">
+      <c r="J339" s="9">
         <v>5.6300000000000003E-2</v>
       </c>
     </row>
@@ -7832,16 +7839,16 @@
         <f t="shared" ref="E340" si="276">E$246+J340</f>
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="G340" s="10">
+      <c r="G340" s="9">
         <v>0.08</v>
       </c>
-      <c r="H340" s="10">
+      <c r="H340" s="9">
         <v>7.6300000000000007E-2</v>
       </c>
-      <c r="I340" s="10">
+      <c r="I340" s="9">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="J340" s="10">
+      <c r="J340" s="9">
         <v>6.1400000000000003E-2</v>
       </c>
     </row>
@@ -7865,16 +7872,16 @@
         <f t="shared" ref="E341" si="280">E$246+J341</f>
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="G341" s="10">
+      <c r="G341" s="9">
         <v>8.14E-2</v>
       </c>
-      <c r="H341" s="10">
+      <c r="H341" s="9">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I341" s="10">
+      <c r="I341" s="9">
         <v>3.4200000000000001E-2</v>
       </c>
-      <c r="J341" s="10">
+      <c r="J341" s="9">
         <v>6.6500000000000004E-2</v>
       </c>
     </row>
@@ -7898,16 +7905,16 @@
         <f t="shared" ref="E342" si="284">E$246+J342</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G342" s="10">
+      <c r="G342" s="9">
         <v>8.5500000000000007E-2</v>
       </c>
-      <c r="H342" s="10">
+      <c r="H342" s="9">
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="I342" s="10">
+      <c r="I342" s="9">
         <v>4.3299999999999998E-2</v>
       </c>
-      <c r="J342" s="10">
+      <c r="J342" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -7931,16 +7938,16 @@
         <f t="shared" ref="E343" si="288">E$246+J343</f>
         <v>6.6100000000000006E-2</v>
       </c>
-      <c r="G343" s="10">
+      <c r="G343" s="9">
         <v>8.3599999999999994E-2</v>
       </c>
-      <c r="H343" s="10">
+      <c r="H343" s="9">
         <v>8.8099999999999998E-2</v>
       </c>
-      <c r="I343" s="10">
+      <c r="I343" s="9">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="J343" s="10">
+      <c r="J343" s="9">
         <v>6.6100000000000006E-2</v>
       </c>
     </row>
@@ -7964,16 +7971,16 @@
         <f t="shared" ref="E344" si="292">E$246+J344</f>
         <v>7.7399999999999997E-2</v>
       </c>
-      <c r="G344" s="10">
+      <c r="G344" s="9">
         <v>8.77E-2</v>
       </c>
-      <c r="H344" s="10">
+      <c r="H344" s="9">
         <v>9.5200000000000007E-2</v>
       </c>
-      <c r="I344" s="10">
+      <c r="I344" s="9">
         <v>4.36E-2</v>
       </c>
-      <c r="J344" s="10">
+      <c r="J344" s="9">
         <v>7.7399999999999997E-2</v>
       </c>
     </row>
@@ -7997,16 +8004,16 @@
         <f t="shared" ref="E345" si="296">E$246+J345</f>
         <v>8.0299999999999996E-2</v>
       </c>
-      <c r="G345" s="10">
+      <c r="G345" s="9">
         <v>8.7400000000000005E-2</v>
       </c>
-      <c r="H345" s="10">
+      <c r="H345" s="9">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="I345" s="10">
+      <c r="I345" s="9">
         <v>4.36E-2</v>
       </c>
-      <c r="J345" s="10">
+      <c r="J345" s="9">
         <v>8.0299999999999996E-2</v>
       </c>
     </row>
@@ -8030,16 +8037,16 @@
         <f t="shared" ref="E346" si="300">E$246+J346</f>
         <v>8.3099999999999993E-2</v>
       </c>
-      <c r="G346" s="10">
+      <c r="G346" s="9">
         <v>8.6499999999999994E-2</v>
       </c>
-      <c r="H346" s="10">
+      <c r="H346" s="9">
         <v>0.1036</v>
       </c>
-      <c r="I346" s="10">
+      <c r="I346" s="9">
         <v>4.53E-2</v>
       </c>
-      <c r="J346" s="10">
+      <c r="J346" s="9">
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
@@ -8063,16 +8070,16 @@
         <f t="shared" ref="E347" si="304">E$246+J347</f>
         <v>8.2900000000000001E-2</v>
       </c>
-      <c r="G347" s="10">
+      <c r="G347" s="9">
         <v>8.6699999999999999E-2</v>
       </c>
-      <c r="H347" s="10">
+      <c r="H347" s="9">
         <v>0.1067</v>
       </c>
-      <c r="I347" s="10">
+      <c r="I347" s="9">
         <v>4.5499999999999999E-2</v>
       </c>
-      <c r="J347" s="10">
+      <c r="J347" s="9">
         <v>8.2900000000000001E-2</v>
       </c>
     </row>
@@ -8096,16 +8103,16 @@
         <f t="shared" ref="E348" si="308">E$246+J348</f>
         <v>7.9600000000000004E-2</v>
       </c>
-      <c r="G348" s="10">
+      <c r="G348" s="9">
         <v>8.8700000000000001E-2</v>
       </c>
-      <c r="H348" s="10">
+      <c r="H348" s="9">
         <v>0.1022</v>
       </c>
-      <c r="I348" s="10">
+      <c r="I348" s="9">
         <v>4.6600000000000003E-2</v>
       </c>
-      <c r="J348" s="10">
+      <c r="J348" s="9">
         <v>7.9600000000000004E-2</v>
       </c>
     </row>
@@ -8129,16 +8136,16 @@
         <f t="shared" ref="E349" si="312">E$246+J349</f>
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="G349" s="10">
+      <c r="G349" s="9">
         <v>6.9900000000000004E-2</v>
       </c>
-      <c r="H349" s="10">
+      <c r="H349" s="9">
         <v>6.4399999999999999E-2</v>
       </c>
-      <c r="I349" s="10">
+      <c r="I349" s="9">
         <v>1.78E-2</v>
       </c>
-      <c r="J349" s="10">
+      <c r="J349" s="9">
         <v>5.1200000000000002E-2</v>
       </c>
     </row>
@@ -8162,16 +8169,16 @@
         <f t="shared" ref="E350" si="316">E$246+J350</f>
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="G350" s="10">
+      <c r="G350" s="9">
         <v>7.2400000000000006E-2</v>
       </c>
-      <c r="H350" s="10">
+      <c r="H350" s="9">
         <v>7.3700000000000002E-2</v>
       </c>
-      <c r="I350" s="10">
+      <c r="I350" s="9">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="J350" s="10">
+      <c r="J350" s="9">
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
@@ -8195,16 +8202,16 @@
         <f t="shared" ref="E351" si="320">E$246+J351</f>
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="G351" s="10">
+      <c r="G351" s="9">
         <v>6.9800000000000001E-2</v>
       </c>
-      <c r="H351" s="10">
+      <c r="H351" s="9">
         <v>6.5100000000000005E-2</v>
       </c>
-      <c r="I351" s="10">
+      <c r="I351" s="9">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="J351" s="10">
+      <c r="J351" s="9">
         <v>5.0500000000000003E-2</v>
       </c>
     </row>
@@ -8228,16 +8235,16 @@
         <f t="shared" ref="E352" si="324">E$246+J352</f>
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="G352" s="10">
+      <c r="G352" s="9">
         <v>6.1199999999999997E-2</v>
       </c>
-      <c r="H352" s="10">
+      <c r="H352" s="9">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="I352" s="10">
+      <c r="I352" s="9">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="J352" s="10">
+      <c r="J352" s="9">
         <v>4.4200000000000003E-2</v>
       </c>
     </row>
@@ -8261,16 +8268,16 @@
         <f t="shared" ref="E353" si="328">E$246+J353</f>
         <v>5.1900000000000002E-2</v>
       </c>
-      <c r="G353" s="10">
+      <c r="G353" s="9">
         <v>7.3499999999999996E-2</v>
       </c>
-      <c r="H353" s="10">
+      <c r="H353" s="9">
         <v>7.5399999999999995E-2</v>
       </c>
-      <c r="I353" s="10">
+      <c r="I353" s="9">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="J353" s="10">
+      <c r="J353" s="9">
         <v>5.1900000000000002E-2</v>
       </c>
     </row>
@@ -8294,16 +8301,16 @@
         <f t="shared" ref="E354" si="332">E$246+J354</f>
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="G354" s="10">
+      <c r="G354" s="9">
         <v>7.5499999999999998E-2</v>
       </c>
-      <c r="H354" s="10">
+      <c r="H354" s="9">
         <v>7.9899999999999999E-2</v>
       </c>
-      <c r="I354" s="10">
+      <c r="I354" s="9">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="J354" s="10">
+      <c r="J354" s="9">
         <v>6.1400000000000003E-2</v>
       </c>
     </row>
@@ -8327,16 +8334,16 @@
         <f t="shared" ref="E355" si="336">E$246+J355</f>
         <v>6.5199999999999994E-2</v>
       </c>
-      <c r="G355" s="10">
+      <c r="G355" s="9">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="H355" s="10">
+      <c r="H355" s="9">
         <v>9.8299999999999998E-2</v>
       </c>
-      <c r="I355" s="10">
+      <c r="I355" s="9">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="J355" s="10">
+      <c r="J355" s="9">
         <v>6.5199999999999994E-2</v>
       </c>
     </row>
@@ -8360,16 +8367,16 @@
         <f t="shared" ref="E356" si="340">E$246+J356</f>
         <v>6.59E-2</v>
       </c>
-      <c r="G356" s="10">
+      <c r="G356" s="9">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="H356" s="10">
+      <c r="H356" s="9">
         <v>8.8900000000000007E-2</v>
       </c>
-      <c r="I356" s="10">
+      <c r="I356" s="9">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="J356" s="10">
+      <c r="J356" s="9">
         <v>6.59E-2</v>
       </c>
     </row>
@@ -8393,16 +8400,16 @@
         <f t="shared" ref="E357" si="344">E$246+J357</f>
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="G357" s="10">
+      <c r="G357" s="9">
         <v>7.6700000000000004E-2</v>
       </c>
-      <c r="H357" s="10">
+      <c r="H357" s="9">
         <v>8.7300000000000003E-2</v>
       </c>
-      <c r="I357" s="10">
+      <c r="I357" s="9">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="J357" s="10">
+      <c r="J357" s="9">
         <v>6.9500000000000006E-2</v>
       </c>
     </row>
@@ -8426,16 +8433,16 @@
         <f t="shared" ref="E358" si="348">E$246+J358</f>
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="G358" s="10">
+      <c r="G358" s="9">
         <v>7.9899999999999999E-2</v>
       </c>
-      <c r="H358" s="10">
+      <c r="H358" s="9">
         <v>9.4200000000000006E-2</v>
       </c>
-      <c r="I358" s="10">
+      <c r="I358" s="9">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="J358" s="10">
+      <c r="J358" s="9">
         <v>7.1099999999999997E-2</v>
       </c>
     </row>
@@ -8459,16 +8466,16 @@
         <f t="shared" ref="E359" si="352">E$246+J359</f>
         <v>7.51E-2</v>
       </c>
-      <c r="G359" s="10">
+      <c r="G359" s="9">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="H359" s="10">
+      <c r="H359" s="9">
         <v>9.2499999999999999E-2</v>
       </c>
-      <c r="I359" s="10">
+      <c r="I359" s="9">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="J359" s="10">
+      <c r="J359" s="9">
         <v>7.51E-2</v>
       </c>
     </row>
@@ -8492,16 +8499,16 @@
         <f t="shared" ref="E360" si="356">E$246+J360</f>
         <v>6.2899999999999998E-2</v>
       </c>
-      <c r="G360" s="10">
+      <c r="G360" s="9">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="H360" s="10">
+      <c r="H360" s="9">
         <v>9.2799999999999994E-2</v>
       </c>
-      <c r="I360" s="10">
+      <c r="I360" s="9">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="J360" s="10">
+      <c r="J360" s="9">
         <v>6.2899999999999998E-2</v>
       </c>
     </row>
@@ -8525,16 +8532,16 @@
         <f t="shared" ref="E361" si="360">E$246+J361</f>
         <v>6.2E-2</v>
       </c>
-      <c r="G361" s="10">
+      <c r="G361" s="9">
         <v>7.2900000000000006E-2</v>
       </c>
-      <c r="H361" s="10">
+      <c r="H361" s="9">
         <v>8.0699999999999994E-2</v>
       </c>
-      <c r="I361" s="10">
+      <c r="I361" s="9">
         <v>2.06E-2</v>
       </c>
-      <c r="J361" s="10">
+      <c r="J361" s="9">
         <v>6.2E-2</v>
       </c>
     </row>
@@ -8558,16 +8565,16 @@
         <f t="shared" ref="E362" si="364">E$246+J362</f>
         <v>6.8099999999999994E-2</v>
       </c>
-      <c r="G362" s="10">
+      <c r="G362" s="9">
         <v>7.2099999999999997E-2</v>
       </c>
-      <c r="H362" s="10">
+      <c r="H362" s="9">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="I362" s="10">
+      <c r="I362" s="9">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="J362" s="10">
+      <c r="J362" s="9">
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
@@ -8591,16 +8598,16 @@
         <f t="shared" ref="E363" si="368">E$246+J363</f>
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="G363" s="10">
+      <c r="G363" s="9">
         <v>7.2099999999999997E-2</v>
       </c>
-      <c r="H363" s="10">
+      <c r="H363" s="9">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="I363" s="10">
+      <c r="I363" s="9">
         <v>2.58E-2</v>
       </c>
-      <c r="J363" s="10">
+      <c r="J363" s="9">
         <v>6.8500000000000005E-2</v>
       </c>
     </row>
@@ -8624,16 +8631,16 @@
         <f t="shared" ref="E364" si="372">E$246+J364</f>
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="G364" s="10">
+      <c r="G364" s="9">
         <v>7.2300000000000003E-2</v>
       </c>
-      <c r="H364" s="10">
+      <c r="H364" s="9">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="I364" s="10">
+      <c r="I364" s="9">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="J364" s="10">
+      <c r="J364" s="9">
         <v>6.8500000000000005E-2</v>
       </c>
     </row>
@@ -8657,39 +8664,576 @@
         <f t="shared" ref="E365" si="376">E$246+J365</f>
         <v>6.8599999999999994E-2</v>
       </c>
-      <c r="G365" s="10">
+      <c r="G365" s="9">
         <v>7.2400000000000006E-2</v>
       </c>
-      <c r="H365" s="10">
+      <c r="H365" s="9">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="I365" s="10">
+      <c r="I365" s="9">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J365" s="10">
+      <c r="J365" s="9">
         <v>6.8599999999999994E-2</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E366" s="9"/>
+      <c r="A366" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B366" s="4">
+        <f t="shared" ref="B366" si="377">B$246+G366</f>
+        <v>0.24230000000000002</v>
+      </c>
+      <c r="C366" s="7">
+        <f t="shared" ref="C366" si="378">C$246+H366</f>
+        <v>0.1973</v>
+      </c>
+      <c r="D366" s="7">
+        <f t="shared" ref="D366" si="379">D$246+I366</f>
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="E366" s="4">
+        <f t="shared" ref="E366" si="380">E$246+J366</f>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="G366" s="9">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="H366" s="9">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I366" s="9">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="J366" s="9">
+        <v>6.8500000000000005E-2</v>
+      </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E367" s="9"/>
+      <c r="A367" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B367" s="4">
+        <f t="shared" ref="B367" si="381">B$246+G367</f>
+        <v>0.24230000000000002</v>
+      </c>
+      <c r="C367" s="7">
+        <f t="shared" ref="C367" si="382">C$246+H367</f>
+        <v>0.1973</v>
+      </c>
+      <c r="D367" s="7">
+        <f t="shared" ref="D367" si="383">D$246+I367</f>
+        <v>0.14549999999999999</v>
+      </c>
+      <c r="E367" s="4">
+        <f t="shared" ref="E367" si="384">E$246+J367</f>
+        <v>6.83E-2</v>
+      </c>
+      <c r="G367" s="9">
+        <v>7.2400000000000006E-2</v>
+      </c>
+      <c r="H367" s="9">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I367" s="9">
+        <v>2.58E-2</v>
+      </c>
+      <c r="J367" s="9">
+        <v>6.83E-2</v>
+      </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E368" s="9"/>
-    </row>
-    <row r="369" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E369" s="9"/>
-    </row>
-    <row r="370" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E370" s="9"/>
-    </row>
-    <row r="371" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E371" s="9"/>
-    </row>
-    <row r="372" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E372" s="9"/>
+      <c r="A368" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B368" s="4">
+        <f t="shared" ref="B368" si="385">B$246+G368</f>
+        <v>0.24209999999999998</v>
+      </c>
+      <c r="C368" s="7">
+        <f t="shared" ref="C368" si="386">C$246+H368</f>
+        <v>0.1973</v>
+      </c>
+      <c r="D368" s="7">
+        <f t="shared" ref="D368" si="387">D$246+I368</f>
+        <v>0.14219999999999999</v>
+      </c>
+      <c r="E368" s="4">
+        <f t="shared" ref="E368" si="388">E$246+J368</f>
+        <v>6.8099999999999994E-2</v>
+      </c>
+      <c r="G368" s="9">
+        <v>7.22E-2</v>
+      </c>
+      <c r="H368" s="9">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I368" s="9">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="J368" s="9">
+        <v>6.8099999999999994E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A369" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B369" s="4">
+        <f t="shared" ref="B369" si="389">B$246+G369</f>
+        <v>0.24819999999999998</v>
+      </c>
+      <c r="C369" s="7">
+        <f t="shared" ref="C369" si="390">C$246+H369</f>
+        <v>0.1973</v>
+      </c>
+      <c r="D369" s="7">
+        <f t="shared" ref="D369" si="391">D$246+I369</f>
+        <v>0.1424</v>
+      </c>
+      <c r="E369" s="4">
+        <f t="shared" ref="E369" si="392">E$246+J369</f>
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="G369" s="9">
+        <v>7.8299999999999995E-2</v>
+      </c>
+      <c r="H369" s="9">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I369" s="9">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="J369" s="9">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="L369" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A370" s="3">
+        <v>46210</v>
+      </c>
+      <c r="B370" s="4">
+        <f t="shared" ref="B370" si="393">B$246+G370</f>
+        <v>0.24819999999999998</v>
+      </c>
+      <c r="C370" s="7">
+        <f t="shared" ref="C370" si="394">C$246+H370</f>
+        <v>0.1973</v>
+      </c>
+      <c r="D370" s="7">
+        <f t="shared" ref="D370" si="395">D$246+I370</f>
+        <v>0.15129999999999999</v>
+      </c>
+      <c r="E370" s="4">
+        <f t="shared" ref="E370" si="396">E$246+J370</f>
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="G370" s="9">
+        <v>7.8299999999999995E-2</v>
+      </c>
+      <c r="H370" s="9">
+        <v>8.14E-2</v>
+      </c>
+      <c r="I370" s="9">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="J370" s="9">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="L370" s="9">
+        <v>2.0799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A371" s="3">
+        <v>46211</v>
+      </c>
+      <c r="B371" s="4">
+        <f t="shared" ref="B371" si="397">B$246+G371</f>
+        <v>0.24819999999999998</v>
+      </c>
+      <c r="C371" s="7">
+        <f>C$246+H371+$L$370</f>
+        <v>0.19729999999999998</v>
+      </c>
+      <c r="D371" s="7">
+        <f t="shared" ref="D371" si="398">D$246+I371</f>
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="E371" s="4">
+        <f t="shared" ref="E371" si="399">E$246+J371</f>
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="G371" s="9">
+        <v>7.8299999999999995E-2</v>
+      </c>
+      <c r="H371" s="9">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="I371" s="9">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="J371" s="9">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="L371" s="9"/>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A372" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B372" s="4">
+        <f t="shared" ref="B372" si="400">B$246+G372</f>
+        <v>0.24529999999999999</v>
+      </c>
+      <c r="C372" s="7">
+        <f>C$246+H372+$L$370</f>
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="D372" s="7">
+        <f t="shared" ref="D372" si="401">D$246+I372</f>
+        <v>0.14300000000000002</v>
+      </c>
+      <c r="E372" s="4">
+        <f t="shared" ref="E372" si="402">E$246+J372</f>
+        <v>5.33E-2</v>
+      </c>
+      <c r="G372" s="9">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="H372" s="9">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="I372" s="9">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="J372" s="9">
+        <v>5.33E-2</v>
+      </c>
+      <c r="L372" s="9"/>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A373" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B373" s="4">
+        <f t="shared" ref="B373" si="403">B$246+G373</f>
+        <v>0.24909999999999999</v>
+      </c>
+      <c r="C373" s="7">
+        <f>C$246+H373+$L$370</f>
+        <v>0.19450000000000001</v>
+      </c>
+      <c r="D373" s="7">
+        <f t="shared" ref="D373" si="404">D$246+I373</f>
+        <v>0.14929999999999999</v>
+      </c>
+      <c r="E373" s="4">
+        <f t="shared" ref="E373" si="405">E$246+J373</f>
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="G373" s="9">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="H373" s="9">
+        <v>5.7799999999999997E-2</v>
+      </c>
+      <c r="I373" s="9">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="J373" s="9">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="L373" s="9"/>
+      <c r="N373" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A374" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B374" s="4">
+        <f t="shared" ref="B374" si="406">B$246+G374</f>
+        <v>0.25180000000000002</v>
+      </c>
+      <c r="C374" s="7">
+        <f>C$246+H374+$L$370</f>
+        <v>0.1956</v>
+      </c>
+      <c r="D374" s="7">
+        <f t="shared" ref="D374" si="407">D$246+I374</f>
+        <v>0.15060000000000001</v>
+      </c>
+      <c r="E374" s="4">
+        <f>E$246+J374+$N$374</f>
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="G374" s="9">
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="H374" s="9">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="I374" s="9">
+        <v>3.09E-2</v>
+      </c>
+      <c r="J374" s="9">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="L374" s="9"/>
+      <c r="N374" s="9">
+        <v>1.55E-2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A375" s="3">
+        <v>46217</v>
+      </c>
+      <c r="B375" s="4">
+        <f t="shared" ref="B375" si="408">B$246+G375</f>
+        <v>0.24679999999999999</v>
+      </c>
+      <c r="C375" s="7">
+        <f>C$246+H375+$L$370</f>
+        <v>0.18240000000000001</v>
+      </c>
+      <c r="D375" s="7">
+        <f t="shared" ref="D375" si="409">D$246+I375</f>
+        <v>0.14150000000000001</v>
+      </c>
+      <c r="E375" s="4">
+        <f>E$246+J375+$N$374</f>
+        <v>4.5700000000000005E-2</v>
+      </c>
+      <c r="G375" s="9">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="H375" s="9">
+        <v>4.5699999999999998E-2</v>
+      </c>
+      <c r="I375" s="9">
+        <v>2.18E-2</v>
+      </c>
+      <c r="J375" s="9">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="L375" s="9"/>
+      <c r="N375" s="9"/>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A376" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B376" s="4">
+        <f t="shared" ref="B376" si="410">B$246+G376</f>
+        <v>0.251</v>
+      </c>
+      <c r="C376" s="7">
+        <f>C$246+H376+$L$370</f>
+        <v>0.19019999999999998</v>
+      </c>
+      <c r="D376" s="7">
+        <f t="shared" ref="D376" si="411">D$246+I376</f>
+        <v>0.1464</v>
+      </c>
+      <c r="E376" s="4">
+        <f>E$246+J376+$N$374</f>
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="G376" s="9">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="H376" s="9">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="I376" s="9">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="J376" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="L376" s="9"/>
+      <c r="N376" s="9"/>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A377" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B377" s="4">
+        <f t="shared" ref="B377" si="412">B$246+G377</f>
+        <v>0.25329999999999997</v>
+      </c>
+      <c r="C377" s="7">
+        <f>C$246+H377+$L$370</f>
+        <v>0.1895</v>
+      </c>
+      <c r="D377" s="7">
+        <f t="shared" ref="D377" si="413">D$246+I377</f>
+        <v>0.1484</v>
+      </c>
+      <c r="E377" s="4">
+        <f>E$246+J377+$N$374</f>
+        <v>4.5700000000000005E-2</v>
+      </c>
+      <c r="G377" s="9">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="H377" s="9">
+        <v>5.28E-2</v>
+      </c>
+      <c r="I377" s="9">
+        <v>2.87E-2</v>
+      </c>
+      <c r="J377" s="9">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="L377" s="9"/>
+      <c r="N377" s="9"/>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A378" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B378" s="4">
+        <f t="shared" ref="B378" si="414">B$246+G378</f>
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="C378" s="7">
+        <f>C$246+H378+$L$370</f>
+        <v>0.17609999999999998</v>
+      </c>
+      <c r="D378" s="7">
+        <f t="shared" ref="D378" si="415">D$246+I378</f>
+        <v>0.13830000000000001</v>
+      </c>
+      <c r="E378" s="4">
+        <f>E$246+J378+$N$374</f>
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="G378" s="9">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H378" s="9">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="I378" s="9">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="J378" s="9">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="L378" s="9"/>
+      <c r="N378" s="9"/>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A379" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B379" s="4">
+        <f t="shared" ref="B379" si="416">B$246+G379</f>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="C379" s="7">
+        <f>C$246+H379+$L$370</f>
+        <v>0.1749</v>
+      </c>
+      <c r="D379" s="7">
+        <f t="shared" ref="D379" si="417">D$246+I379</f>
+        <v>0.13519999999999999</v>
+      </c>
+      <c r="E379" s="4">
+        <f>E$246+J379+$N$374</f>
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="G379" s="9">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="H379" s="9">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="I379" s="9">
+        <v>1.55E-2</v>
+      </c>
+      <c r="J379" s="9">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="L379" s="9"/>
+      <c r="N379" s="9"/>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A380" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B380" s="4">
+        <f t="shared" ref="B380" si="418">B$246+G380</f>
+        <v>0.24959999999999999</v>
+      </c>
+      <c r="C380" s="7">
+        <f>C$246+H380+$L$370</f>
+        <v>0.18530000000000002</v>
+      </c>
+      <c r="D380" s="7">
+        <f t="shared" ref="D380" si="419">D$246+I380</f>
+        <v>0.14250000000000002</v>
+      </c>
+      <c r="E380" s="4">
+        <f>E$246+J380+$N$374</f>
+        <v>4.53E-2</v>
+      </c>
+      <c r="G380" s="9">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="H380" s="9">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="I380" s="9">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J380" s="9">
+        <v>2.98E-2</v>
+      </c>
+      <c r="L380" s="9"/>
+      <c r="N380" s="9"/>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A381" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B381" s="4">
+        <f t="shared" ref="B381" si="420">B$246+G381</f>
+        <v>0.24919999999999998</v>
+      </c>
+      <c r="C381" s="7">
+        <f>C$246+H381+$L$370</f>
+        <v>0.184</v>
+      </c>
+      <c r="D381" s="7">
+        <f t="shared" ref="D381" si="421">D$246+I381</f>
+        <v>0.14019999999999999</v>
+      </c>
+      <c r="E381" s="4">
+        <f>E$246+J381+$N$374</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G381" s="9">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="H381" s="9">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="I381" s="9">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="J381" s="9">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="L381" s="9"/>
+      <c r="N381" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC2583A-27CC-4AF6-93B4-E7013CB61CBF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4703A7DE-6849-440B-84C6-D236B30B421D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S381"/>
+  <dimension ref="A1:S384"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -8857,15 +8857,15 @@
         <v>0.24819999999999998</v>
       </c>
       <c r="C371" s="7">
-        <f>C$246+H371+$L$370</f>
+        <f t="shared" ref="C371:C381" si="398">C$246+H371+$L$370</f>
         <v>0.19729999999999998</v>
       </c>
       <c r="D371" s="7">
-        <f t="shared" ref="D371" si="398">D$246+I371</f>
+        <f t="shared" ref="D371" si="399">D$246+I371</f>
         <v>0.14360000000000001</v>
       </c>
       <c r="E371" s="4">
-        <f t="shared" ref="E371" si="399">E$246+J371</f>
+        <f t="shared" ref="E371" si="400">E$246+J371</f>
         <v>5.3400000000000003E-2</v>
       </c>
       <c r="G371" s="9">
@@ -8887,19 +8887,19 @@
         <v>46212</v>
       </c>
       <c r="B372" s="4">
-        <f t="shared" ref="B372" si="400">B$246+G372</f>
+        <f t="shared" ref="B372" si="401">B$246+G372</f>
         <v>0.24529999999999999</v>
       </c>
       <c r="C372" s="7">
-        <f>C$246+H372+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.18790000000000001</v>
       </c>
       <c r="D372" s="7">
-        <f t="shared" ref="D372" si="401">D$246+I372</f>
+        <f t="shared" ref="D372" si="402">D$246+I372</f>
         <v>0.14300000000000002</v>
       </c>
       <c r="E372" s="4">
-        <f t="shared" ref="E372" si="402">E$246+J372</f>
+        <f t="shared" ref="E372" si="403">E$246+J372</f>
         <v>5.33E-2</v>
       </c>
       <c r="G372" s="9">
@@ -8921,19 +8921,19 @@
         <v>46213</v>
       </c>
       <c r="B373" s="4">
-        <f t="shared" ref="B373" si="403">B$246+G373</f>
+        <f t="shared" ref="B373" si="404">B$246+G373</f>
         <v>0.24909999999999999</v>
       </c>
       <c r="C373" s="7">
-        <f>C$246+H373+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.19450000000000001</v>
       </c>
       <c r="D373" s="7">
-        <f t="shared" ref="D373" si="404">D$246+I373</f>
+        <f t="shared" ref="D373" si="405">D$246+I373</f>
         <v>0.14929999999999999</v>
       </c>
       <c r="E373" s="4">
-        <f t="shared" ref="E373" si="405">E$246+J373</f>
+        <f t="shared" ref="E373" si="406">E$246+J373</f>
         <v>5.6399999999999999E-2</v>
       </c>
       <c r="G373" s="9">
@@ -8958,19 +8958,19 @@
         <v>46216</v>
       </c>
       <c r="B374" s="4">
-        <f t="shared" ref="B374" si="406">B$246+G374</f>
+        <f t="shared" ref="B374" si="407">B$246+G374</f>
         <v>0.25180000000000002</v>
       </c>
       <c r="C374" s="7">
-        <f>C$246+H374+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.1956</v>
       </c>
       <c r="D374" s="7">
-        <f t="shared" ref="D374" si="407">D$246+I374</f>
+        <f t="shared" ref="D374" si="408">D$246+I374</f>
         <v>0.15060000000000001</v>
       </c>
       <c r="E374" s="4">
-        <f>E$246+J374+$N$374</f>
+        <f t="shared" ref="E374:E381" si="409">E$246+J374+$N$374</f>
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="G374" s="9">
@@ -8995,19 +8995,19 @@
         <v>46217</v>
       </c>
       <c r="B375" s="4">
-        <f t="shared" ref="B375" si="408">B$246+G375</f>
+        <f t="shared" ref="B375" si="410">B$246+G375</f>
         <v>0.24679999999999999</v>
       </c>
       <c r="C375" s="7">
-        <f>C$246+H375+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.18240000000000001</v>
       </c>
       <c r="D375" s="7">
-        <f t="shared" ref="D375" si="409">D$246+I375</f>
+        <f t="shared" ref="D375" si="411">D$246+I375</f>
         <v>0.14150000000000001</v>
       </c>
       <c r="E375" s="4">
-        <f>E$246+J375+$N$374</f>
+        <f t="shared" si="409"/>
         <v>4.5700000000000005E-2</v>
       </c>
       <c r="G375" s="9">
@@ -9030,19 +9030,19 @@
         <v>46218</v>
       </c>
       <c r="B376" s="4">
-        <f t="shared" ref="B376" si="410">B$246+G376</f>
+        <f t="shared" ref="B376" si="412">B$246+G376</f>
         <v>0.251</v>
       </c>
       <c r="C376" s="7">
-        <f>C$246+H376+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.19019999999999998</v>
       </c>
       <c r="D376" s="7">
-        <f t="shared" ref="D376" si="411">D$246+I376</f>
+        <f t="shared" ref="D376" si="413">D$246+I376</f>
         <v>0.1464</v>
       </c>
       <c r="E376" s="4">
-        <f>E$246+J376+$N$374</f>
+        <f t="shared" si="409"/>
         <v>4.8500000000000001E-2</v>
       </c>
       <c r="G376" s="9">
@@ -9065,19 +9065,19 @@
         <v>46219</v>
       </c>
       <c r="B377" s="4">
-        <f t="shared" ref="B377" si="412">B$246+G377</f>
+        <f t="shared" ref="B377" si="414">B$246+G377</f>
         <v>0.25329999999999997</v>
       </c>
       <c r="C377" s="7">
-        <f>C$246+H377+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.1895</v>
       </c>
       <c r="D377" s="7">
-        <f t="shared" ref="D377" si="413">D$246+I377</f>
+        <f t="shared" ref="D377" si="415">D$246+I377</f>
         <v>0.1484</v>
       </c>
       <c r="E377" s="4">
-        <f>E$246+J377+$N$374</f>
+        <f t="shared" si="409"/>
         <v>4.5700000000000005E-2</v>
       </c>
       <c r="G377" s="9">
@@ -9100,19 +9100,19 @@
         <v>46223</v>
       </c>
       <c r="B378" s="4">
-        <f t="shared" ref="B378" si="414">B$246+G378</f>
+        <f t="shared" ref="B378" si="416">B$246+G378</f>
         <v>0.24390000000000001</v>
       </c>
       <c r="C378" s="7">
-        <f>C$246+H378+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.17609999999999998</v>
       </c>
       <c r="D378" s="7">
-        <f t="shared" ref="D378" si="415">D$246+I378</f>
+        <f t="shared" ref="D378" si="417">D$246+I378</f>
         <v>0.13830000000000001</v>
       </c>
       <c r="E378" s="4">
-        <f>E$246+J378+$N$374</f>
+        <f t="shared" si="409"/>
         <v>3.5799999999999998E-2</v>
       </c>
       <c r="G378" s="9">
@@ -9135,19 +9135,19 @@
         <v>46224</v>
       </c>
       <c r="B379" s="4">
-        <f t="shared" ref="B379" si="416">B$246+G379</f>
+        <f t="shared" ref="B379" si="418">B$246+G379</f>
         <v>0.24299999999999999</v>
       </c>
       <c r="C379" s="7">
-        <f>C$246+H379+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.1749</v>
       </c>
       <c r="D379" s="7">
-        <f t="shared" ref="D379" si="417">D$246+I379</f>
+        <f t="shared" ref="D379" si="419">D$246+I379</f>
         <v>0.13519999999999999</v>
       </c>
       <c r="E379" s="4">
-        <f>E$246+J379+$N$374</f>
+        <f t="shared" si="409"/>
         <v>3.9800000000000002E-2</v>
       </c>
       <c r="G379" s="9">
@@ -9170,19 +9170,19 @@
         <v>46225</v>
       </c>
       <c r="B380" s="4">
-        <f t="shared" ref="B380" si="418">B$246+G380</f>
+        <f t="shared" ref="B380" si="420">B$246+G380</f>
         <v>0.24959999999999999</v>
       </c>
       <c r="C380" s="7">
-        <f>C$246+H380+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.18530000000000002</v>
       </c>
       <c r="D380" s="7">
-        <f t="shared" ref="D380" si="419">D$246+I380</f>
+        <f t="shared" ref="D380" si="421">D$246+I380</f>
         <v>0.14250000000000002</v>
       </c>
       <c r="E380" s="4">
-        <f>E$246+J380+$N$374</f>
+        <f t="shared" si="409"/>
         <v>4.53E-2</v>
       </c>
       <c r="G380" s="9">
@@ -9205,19 +9205,19 @@
         <v>46226</v>
       </c>
       <c r="B381" s="4">
-        <f t="shared" ref="B381" si="420">B$246+G381</f>
+        <f t="shared" ref="B381" si="422">B$246+G381</f>
         <v>0.24919999999999998</v>
       </c>
       <c r="C381" s="7">
-        <f>C$246+H381+$L$370</f>
+        <f t="shared" si="398"/>
         <v>0.184</v>
       </c>
       <c r="D381" s="7">
-        <f t="shared" ref="D381" si="421">D$246+I381</f>
+        <f t="shared" ref="D381" si="423">D$246+I381</f>
         <v>0.14019999999999999</v>
       </c>
       <c r="E381" s="4">
-        <f>E$246+J381+$N$374</f>
+        <f t="shared" si="409"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G381" s="9">
@@ -9234,6 +9234,111 @@
       </c>
       <c r="L381" s="9"/>
       <c r="N381" s="9"/>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A382" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B382" s="4">
+        <f t="shared" ref="B382" si="424">B$246+G382</f>
+        <v>0.245</v>
+      </c>
+      <c r="C382" s="7">
+        <f t="shared" ref="C382" si="425">C$246+H382+$L$370</f>
+        <v>0.18109999999999998</v>
+      </c>
+      <c r="D382" s="7">
+        <f t="shared" ref="D382" si="426">D$246+I382</f>
+        <v>0.1338</v>
+      </c>
+      <c r="E382" s="4">
+        <f t="shared" ref="E382" si="427">E$246+J382+$N$374</f>
+        <v>3.6500000000000005E-2</v>
+      </c>
+      <c r="G382" s="9">
+        <v>7.51E-2</v>
+      </c>
+      <c r="H382" s="9">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="I382" s="9">
+        <v>1.41E-2</v>
+      </c>
+      <c r="J382" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="L382" s="9"/>
+      <c r="N382" s="9"/>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A383" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B383" s="4">
+        <f t="shared" ref="B383" si="428">B$246+G383</f>
+        <v>0.24440000000000001</v>
+      </c>
+      <c r="C383" s="7">
+        <f t="shared" ref="C383" si="429">C$246+H383+$L$370</f>
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="D383" s="7">
+        <f t="shared" ref="D383" si="430">D$246+I383</f>
+        <v>0.1338</v>
+      </c>
+      <c r="E383" s="4">
+        <f t="shared" ref="E383" si="431">E$246+J383+$N$374</f>
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="G383" s="9">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="H383" s="9">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="I383" s="9">
+        <v>1.41E-2</v>
+      </c>
+      <c r="J383" s="9">
+        <v>2.53E-2</v>
+      </c>
+      <c r="L383" s="9"/>
+      <c r="N383" s="9"/>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A384" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B384" s="4">
+        <f t="shared" ref="B384" si="432">B$246+G384</f>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="C384" s="7">
+        <f t="shared" ref="C384" si="433">C$246+H384+$L$370</f>
+        <v>0.17620000000000002</v>
+      </c>
+      <c r="D384" s="7">
+        <f t="shared" ref="D384" si="434">D$246+I384</f>
+        <v>0.1361</v>
+      </c>
+      <c r="E384" s="4">
+        <f t="shared" ref="E384" si="435">E$246+J384+$N$374</f>
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="G384" s="9">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="H384" s="9">
+        <v>3.95E-2</v>
+      </c>
+      <c r="I384" s="9">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="J384" s="9">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="L384" s="9"/>
+      <c r="N384" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4703A7DE-6849-440B-84C6-D236B30B421D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A514A749-1A99-4FD9-B861-44F11305D408}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S384"/>
+  <dimension ref="A1:S385"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -9340,6 +9340,41 @@
       <c r="L384" s="9"/>
       <c r="N384" s="9"/>
     </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A385" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B385" s="4">
+        <f t="shared" ref="B385" si="436">B$246+G385</f>
+        <v>0.2419</v>
+      </c>
+      <c r="C385" s="7">
+        <f t="shared" ref="C385" si="437">C$246+H385+$L$370</f>
+        <v>0.17049999999999998</v>
+      </c>
+      <c r="D385" s="7">
+        <f t="shared" ref="D385" si="438">D$246+I385</f>
+        <v>0.1363</v>
+      </c>
+      <c r="E385" s="4">
+        <f t="shared" ref="E385" si="439">E$246+J385+$N$374</f>
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="G385" s="9">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="H385" s="9">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="I385" s="9">
+        <v>1.66E-2</v>
+      </c>
+      <c r="J385" s="9">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="L385" s="9"/>
+      <c r="N385" s="9"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A514A749-1A99-4FD9-B861-44F11305D408}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB24C665-8D59-47B5-AA30-26F64D6F3792}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,12 +111,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -142,7 +148,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -173,6 +179,36 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -558,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S385"/>
+  <dimension ref="A1:S403"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -8825,11 +8861,11 @@
         <v>0.1973</v>
       </c>
       <c r="D370" s="7">
-        <f t="shared" ref="D370" si="395">D$246+I370</f>
+        <f>D$246+I370</f>
         <v>0.15129999999999999</v>
       </c>
       <c r="E370" s="4">
-        <f t="shared" ref="E370" si="396">E$246+J370</f>
+        <f t="shared" ref="E370" si="395">E$246+J370</f>
         <v>6.4399999999999999E-2</v>
       </c>
       <c r="G370" s="9">
@@ -8853,19 +8889,19 @@
         <v>46211</v>
       </c>
       <c r="B371" s="4">
-        <f t="shared" ref="B371" si="397">B$246+G371</f>
+        <f t="shared" ref="B371" si="396">B$246+G371</f>
         <v>0.24819999999999998</v>
       </c>
       <c r="C371" s="7">
-        <f t="shared" ref="C371:C381" si="398">C$246+H371+$L$370</f>
+        <f>C$246+H371+$L$370</f>
         <v>0.19729999999999998</v>
       </c>
       <c r="D371" s="7">
-        <f t="shared" ref="D371" si="399">D$246+I371</f>
+        <f t="shared" ref="D371" si="397">D$246+I371</f>
         <v>0.14360000000000001</v>
       </c>
       <c r="E371" s="4">
-        <f t="shared" ref="E371" si="400">E$246+J371</f>
+        <f t="shared" ref="E371" si="398">E$246+J371</f>
         <v>5.3400000000000003E-2</v>
       </c>
       <c r="G371" s="9">
@@ -8887,19 +8923,19 @@
         <v>46212</v>
       </c>
       <c r="B372" s="4">
-        <f t="shared" ref="B372" si="401">B$246+G372</f>
+        <f t="shared" ref="B372" si="399">B$246+G372</f>
         <v>0.24529999999999999</v>
       </c>
       <c r="C372" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" ref="C371:C381" si="400">C$246+H372+$L$370</f>
         <v>0.18790000000000001</v>
       </c>
       <c r="D372" s="7">
-        <f t="shared" ref="D372" si="402">D$246+I372</f>
+        <f t="shared" ref="D372" si="401">D$246+I372</f>
         <v>0.14300000000000002</v>
       </c>
       <c r="E372" s="4">
-        <f t="shared" ref="E372" si="403">E$246+J372</f>
+        <f t="shared" ref="E372" si="402">E$246+J372</f>
         <v>5.33E-2</v>
       </c>
       <c r="G372" s="9">
@@ -8921,19 +8957,19 @@
         <v>46213</v>
       </c>
       <c r="B373" s="4">
-        <f t="shared" ref="B373" si="404">B$246+G373</f>
+        <f t="shared" ref="B373" si="403">B$246+G373</f>
         <v>0.24909999999999999</v>
       </c>
       <c r="C373" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.19450000000000001</v>
       </c>
       <c r="D373" s="7">
-        <f t="shared" ref="D373" si="405">D$246+I373</f>
+        <f t="shared" ref="D373" si="404">D$246+I373</f>
         <v>0.14929999999999999</v>
       </c>
       <c r="E373" s="4">
-        <f t="shared" ref="E373" si="406">E$246+J373</f>
+        <f t="shared" ref="E373" si="405">E$246+J373</f>
         <v>5.6399999999999999E-2</v>
       </c>
       <c r="G373" s="9">
@@ -8958,19 +8994,19 @@
         <v>46216</v>
       </c>
       <c r="B374" s="4">
-        <f t="shared" ref="B374" si="407">B$246+G374</f>
+        <f t="shared" ref="B374" si="406">B$246+G374</f>
         <v>0.25180000000000002</v>
       </c>
       <c r="C374" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.1956</v>
       </c>
       <c r="D374" s="7">
-        <f t="shared" ref="D374" si="408">D$246+I374</f>
+        <f t="shared" ref="D374" si="407">D$246+I374</f>
         <v>0.15060000000000001</v>
       </c>
       <c r="E374" s="4">
-        <f t="shared" ref="E374:E381" si="409">E$246+J374+$N$374</f>
+        <f>E$246+J374+$N$374</f>
         <v>4.7300000000000002E-2</v>
       </c>
       <c r="G374" s="9">
@@ -8995,19 +9031,19 @@
         <v>46217</v>
       </c>
       <c r="B375" s="4">
-        <f t="shared" ref="B375" si="410">B$246+G375</f>
+        <f t="shared" ref="B375" si="408">B$246+G375</f>
         <v>0.24679999999999999</v>
       </c>
       <c r="C375" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.18240000000000001</v>
       </c>
       <c r="D375" s="7">
-        <f t="shared" ref="D375" si="411">D$246+I375</f>
+        <f t="shared" ref="D375" si="409">D$246+I375</f>
         <v>0.14150000000000001</v>
       </c>
       <c r="E375" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" ref="E374:E381" si="410">E$246+J375+$N$374</f>
         <v>4.5700000000000005E-2</v>
       </c>
       <c r="G375" s="9">
@@ -9030,19 +9066,19 @@
         <v>46218</v>
       </c>
       <c r="B376" s="4">
-        <f t="shared" ref="B376" si="412">B$246+G376</f>
+        <f t="shared" ref="B376" si="411">B$246+G376</f>
         <v>0.251</v>
       </c>
       <c r="C376" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.19019999999999998</v>
       </c>
       <c r="D376" s="7">
-        <f t="shared" ref="D376" si="413">D$246+I376</f>
+        <f t="shared" ref="D376" si="412">D$246+I376</f>
         <v>0.1464</v>
       </c>
       <c r="E376" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>4.8500000000000001E-2</v>
       </c>
       <c r="G376" s="9">
@@ -9065,19 +9101,19 @@
         <v>46219</v>
       </c>
       <c r="B377" s="4">
-        <f t="shared" ref="B377" si="414">B$246+G377</f>
+        <f t="shared" ref="B377" si="413">B$246+G377</f>
         <v>0.25329999999999997</v>
       </c>
       <c r="C377" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.1895</v>
       </c>
       <c r="D377" s="7">
-        <f t="shared" ref="D377" si="415">D$246+I377</f>
+        <f t="shared" ref="D377" si="414">D$246+I377</f>
         <v>0.1484</v>
       </c>
       <c r="E377" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>4.5700000000000005E-2</v>
       </c>
       <c r="G377" s="9">
@@ -9100,19 +9136,19 @@
         <v>46223</v>
       </c>
       <c r="B378" s="4">
-        <f t="shared" ref="B378" si="416">B$246+G378</f>
+        <f t="shared" ref="B378" si="415">B$246+G378</f>
         <v>0.24390000000000001</v>
       </c>
       <c r="C378" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.17609999999999998</v>
       </c>
       <c r="D378" s="7">
-        <f t="shared" ref="D378" si="417">D$246+I378</f>
+        <f t="shared" ref="D378" si="416">D$246+I378</f>
         <v>0.13830000000000001</v>
       </c>
       <c r="E378" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>3.5799999999999998E-2</v>
       </c>
       <c r="G378" s="9">
@@ -9135,19 +9171,19 @@
         <v>46224</v>
       </c>
       <c r="B379" s="4">
-        <f t="shared" ref="B379" si="418">B$246+G379</f>
+        <f t="shared" ref="B379" si="417">B$246+G379</f>
         <v>0.24299999999999999</v>
       </c>
       <c r="C379" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.1749</v>
       </c>
       <c r="D379" s="7">
-        <f t="shared" ref="D379" si="419">D$246+I379</f>
+        <f t="shared" ref="D379" si="418">D$246+I379</f>
         <v>0.13519999999999999</v>
       </c>
       <c r="E379" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>3.9800000000000002E-2</v>
       </c>
       <c r="G379" s="9">
@@ -9170,19 +9206,19 @@
         <v>46225</v>
       </c>
       <c r="B380" s="4">
-        <f t="shared" ref="B380" si="420">B$246+G380</f>
+        <f t="shared" ref="B380" si="419">B$246+G380</f>
         <v>0.24959999999999999</v>
       </c>
       <c r="C380" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.18530000000000002</v>
       </c>
       <c r="D380" s="7">
-        <f t="shared" ref="D380" si="421">D$246+I380</f>
+        <f t="shared" ref="D380" si="420">D$246+I380</f>
         <v>0.14250000000000002</v>
       </c>
       <c r="E380" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>4.53E-2</v>
       </c>
       <c r="G380" s="9">
@@ -9205,19 +9241,19 @@
         <v>46226</v>
       </c>
       <c r="B381" s="4">
-        <f t="shared" ref="B381" si="422">B$246+G381</f>
+        <f t="shared" ref="B381" si="421">B$246+G381</f>
         <v>0.24919999999999998</v>
       </c>
       <c r="C381" s="7">
-        <f t="shared" si="398"/>
+        <f t="shared" si="400"/>
         <v>0.184</v>
       </c>
       <c r="D381" s="7">
-        <f t="shared" ref="D381" si="423">D$246+I381</f>
+        <f t="shared" ref="D381" si="422">D$246+I381</f>
         <v>0.14019999999999999</v>
       </c>
       <c r="E381" s="4">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G381" s="9">
@@ -9240,19 +9276,19 @@
         <v>46227</v>
       </c>
       <c r="B382" s="4">
-        <f t="shared" ref="B382" si="424">B$246+G382</f>
+        <f t="shared" ref="B382" si="423">B$246+G382</f>
         <v>0.245</v>
       </c>
       <c r="C382" s="7">
-        <f t="shared" ref="C382" si="425">C$246+H382+$L$370</f>
+        <f t="shared" ref="C382" si="424">C$246+H382+$L$370</f>
         <v>0.18109999999999998</v>
       </c>
       <c r="D382" s="7">
-        <f t="shared" ref="D382" si="426">D$246+I382</f>
+        <f t="shared" ref="D382" si="425">D$246+I382</f>
         <v>0.1338</v>
       </c>
       <c r="E382" s="4">
-        <f t="shared" ref="E382" si="427">E$246+J382+$N$374</f>
+        <f t="shared" ref="E382" si="426">E$246+J382+$N$374</f>
         <v>3.6500000000000005E-2</v>
       </c>
       <c r="G382" s="9">
@@ -9275,19 +9311,19 @@
         <v>46230</v>
       </c>
       <c r="B383" s="4">
-        <f t="shared" ref="B383" si="428">B$246+G383</f>
+        <f t="shared" ref="B383" si="427">B$246+G383</f>
         <v>0.24440000000000001</v>
       </c>
       <c r="C383" s="7">
-        <f t="shared" ref="C383" si="429">C$246+H383+$L$370</f>
+        <f t="shared" ref="C383" si="428">C$246+H383+$L$370</f>
         <v>0.17649999999999999</v>
       </c>
       <c r="D383" s="7">
-        <f t="shared" ref="D383" si="430">D$246+I383</f>
+        <f t="shared" ref="D383" si="429">D$246+I383</f>
         <v>0.1338</v>
       </c>
       <c r="E383" s="4">
-        <f t="shared" ref="E383" si="431">E$246+J383+$N$374</f>
+        <f t="shared" ref="E383" si="430">E$246+J383+$N$374</f>
         <v>4.0800000000000003E-2</v>
       </c>
       <c r="G383" s="9">
@@ -9310,19 +9346,19 @@
         <v>46231</v>
       </c>
       <c r="B384" s="4">
-        <f t="shared" ref="B384" si="432">B$246+G384</f>
+        <f t="shared" ref="B384" si="431">B$246+G384</f>
         <v>0.24299999999999999</v>
       </c>
       <c r="C384" s="7">
-        <f t="shared" ref="C384" si="433">C$246+H384+$L$370</f>
+        <f t="shared" ref="C384" si="432">C$246+H384+$L$370</f>
         <v>0.17620000000000002</v>
       </c>
       <c r="D384" s="7">
-        <f t="shared" ref="D384" si="434">D$246+I384</f>
+        <f t="shared" ref="D384" si="433">D$246+I384</f>
         <v>0.1361</v>
       </c>
       <c r="E384" s="4">
-        <f t="shared" ref="E384" si="435">E$246+J384+$N$374</f>
+        <f t="shared" ref="E384" si="434">E$246+J384+$N$374</f>
         <v>3.1899999999999998E-2</v>
       </c>
       <c r="G384" s="9">
@@ -9345,19 +9381,19 @@
         <v>46232</v>
       </c>
       <c r="B385" s="4">
-        <f t="shared" ref="B385" si="436">B$246+G385</f>
+        <f t="shared" ref="B385" si="435">B$246+G385</f>
         <v>0.2419</v>
       </c>
       <c r="C385" s="7">
-        <f t="shared" ref="C385" si="437">C$246+H385+$L$370</f>
+        <f t="shared" ref="C385" si="436">C$246+H385+$L$370</f>
         <v>0.17049999999999998</v>
       </c>
       <c r="D385" s="7">
-        <f t="shared" ref="D385" si="438">D$246+I385</f>
+        <f t="shared" ref="D385" si="437">D$246+I385</f>
         <v>0.1363</v>
       </c>
       <c r="E385" s="4">
-        <f t="shared" ref="E385" si="439">E$246+J385+$N$374</f>
+        <f t="shared" ref="E385" si="438">E$246+J385+$N$374</f>
         <v>2.7099999999999999E-2</v>
       </c>
       <c r="G385" s="9">
@@ -9374,6 +9410,640 @@
       </c>
       <c r="L385" s="9"/>
       <c r="N385" s="9"/>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A386" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B386" s="4">
+        <f t="shared" ref="B386" si="439">B$246+G386</f>
+        <v>0.23669999999999999</v>
+      </c>
+      <c r="C386" s="7">
+        <f t="shared" ref="C386" si="440">C$246+H386+$L$370</f>
+        <v>0.1618</v>
+      </c>
+      <c r="D386" s="7">
+        <f t="shared" ref="D386" si="441">D$246+I386</f>
+        <v>0.12479999999999999</v>
+      </c>
+      <c r="E386" s="4">
+        <f t="shared" ref="E386" si="442">E$246+J386+$N$374</f>
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="G386" s="9">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="H386" s="9">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="I386" s="9">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="J386" s="9">
+        <v>3.8E-3</v>
+      </c>
+      <c r="L386" s="9"/>
+      <c r="N386" s="9"/>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A387" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B387" s="4">
+        <f t="shared" ref="B387" si="443">B$246+G387</f>
+        <v>0.24479999999999999</v>
+      </c>
+      <c r="C387" s="7">
+        <f t="shared" ref="C387" si="444">C$246+H387+$L$370</f>
+        <v>0.1799</v>
+      </c>
+      <c r="D387" s="7">
+        <f t="shared" ref="D387" si="445">D$246+I387</f>
+        <v>0.13830000000000001</v>
+      </c>
+      <c r="E387" s="4">
+        <f t="shared" ref="E387" si="446">E$246+J387+$N$374</f>
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="G387" s="9">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="H387" s="9">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="I387" s="9">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="J387" s="9">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="L387" s="9"/>
+      <c r="N387" s="9"/>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A388" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B388" s="4">
+        <f t="shared" ref="B388" si="447">B$246+G388</f>
+        <v>0.24819999999999998</v>
+      </c>
+      <c r="C388" s="7">
+        <f t="shared" ref="C388" si="448">C$246+H388+$L$370</f>
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="D388" s="7">
+        <f t="shared" ref="D388" si="449">D$246+I388</f>
+        <v>0.1394</v>
+      </c>
+      <c r="E388" s="4">
+        <f t="shared" ref="E388" si="450">E$246+J388+$N$374</f>
+        <v>3.27E-2</v>
+      </c>
+      <c r="G388" s="9">
+        <v>7.8299999999999995E-2</v>
+      </c>
+      <c r="H388" s="9">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="I388" s="9">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="J388" s="9">
+        <v>1.72E-2</v>
+      </c>
+      <c r="L388" s="9"/>
+      <c r="N388" s="9"/>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A389" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B389" s="4">
+        <f t="shared" ref="B389" si="451">B$246+G389</f>
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="C389" s="7">
+        <f t="shared" ref="C389" si="452">C$246+H389+$L$370</f>
+        <v>0.18719999999999998</v>
+      </c>
+      <c r="D389" s="7">
+        <f t="shared" ref="D389" si="453">D$246+I389</f>
+        <v>0.1469</v>
+      </c>
+      <c r="E389" s="4">
+        <f t="shared" ref="E389" si="454">E$246+J389+$N$374</f>
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="G389" s="9">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="H389" s="9">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="I389" s="9">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="J389" s="9">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="L389" s="9"/>
+      <c r="N389" s="9"/>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A390" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B390" s="4">
+        <f t="shared" ref="B390" si="455">B$246+G390</f>
+        <v>0.26339999999999997</v>
+      </c>
+      <c r="C390" s="7">
+        <f t="shared" ref="C390" si="456">C$246+H390+$L$370</f>
+        <v>0.2031</v>
+      </c>
+      <c r="D390" s="7">
+        <f t="shared" ref="D390" si="457">D$246+I390</f>
+        <v>0.16159999999999999</v>
+      </c>
+      <c r="E390" s="4">
+        <f t="shared" ref="E390" si="458">E$246+J390+$N$374</f>
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="G390" s="9">
+        <v>9.35E-2</v>
+      </c>
+      <c r="H390" s="9">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="I390" s="9">
+        <v>4.19E-2</v>
+      </c>
+      <c r="J390" s="9">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="L390" s="9"/>
+      <c r="N390" s="9"/>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A391" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B391" s="17">
+        <f t="shared" ref="B391" si="459">B$246+G391</f>
+        <v>0.26290000000000002</v>
+      </c>
+      <c r="C391" s="18">
+        <f t="shared" ref="C391" si="460">C$246+H391+$L$370</f>
+        <v>0.20429999999999998</v>
+      </c>
+      <c r="D391" s="18">
+        <f t="shared" ref="D391" si="461">D$246+I391</f>
+        <v>0.16209999999999999</v>
+      </c>
+      <c r="E391" s="17">
+        <f t="shared" ref="E391" si="462">E$246+J391+$N$374</f>
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="F391" s="19"/>
+      <c r="G391" s="20">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="H391" s="20">
+        <v>6.7599999999999993E-2</v>
+      </c>
+      <c r="I391" s="20">
+        <v>4.24E-2</v>
+      </c>
+      <c r="J391" s="20">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="L391" s="9"/>
+      <c r="N391" s="9"/>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A392" s="11">
+        <v>46241</v>
+      </c>
+      <c r="B392" s="12">
+        <f t="shared" ref="B392" si="463">B$246+G392</f>
+        <v>0.2616</v>
+      </c>
+      <c r="C392" s="13">
+        <f t="shared" ref="C392" si="464">C$246+H392+$L$370</f>
+        <v>0.20169999999999999</v>
+      </c>
+      <c r="D392" s="13">
+        <f t="shared" ref="D392" si="465">D$246+I392</f>
+        <v>0.1585</v>
+      </c>
+      <c r="E392" s="12">
+        <f>E$246+J392+$N$374+$N$392</f>
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="F392" s="14"/>
+      <c r="G392" s="15">
+        <v>9.1700000000000004E-2</v>
+      </c>
+      <c r="H392" s="15">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I392" s="15">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="J392" s="15">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="L392" s="9"/>
+      <c r="N392" s="9">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A393" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B393" s="4">
+        <f t="shared" ref="B393" si="466">B$246+G393</f>
+        <v>0.26679999999999998</v>
+      </c>
+      <c r="C393" s="7">
+        <f t="shared" ref="C393" si="467">C$246+H393+$L$370</f>
+        <v>0.20900000000000002</v>
+      </c>
+      <c r="D393" s="7">
+        <f t="shared" ref="D393" si="468">D$246+I393</f>
+        <v>0.1646</v>
+      </c>
+      <c r="E393" s="4">
+        <f>E$246+J393+$N$374+N392</f>
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="G393" s="9">
+        <v>9.69E-2</v>
+      </c>
+      <c r="H393" s="9">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="I393" s="9">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="J393" s="9">
+        <v>3.1E-2</v>
+      </c>
+      <c r="L393" s="9"/>
+      <c r="N393" s="9"/>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A394" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B394" s="4">
+        <f t="shared" ref="B394" si="469">B$246+G394</f>
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="C394" s="7">
+        <f t="shared" ref="C394" si="470">C$246+H394+$L$370</f>
+        <v>0.20729999999999998</v>
+      </c>
+      <c r="D394" s="7">
+        <f t="shared" ref="D394" si="471">D$246+I394</f>
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="E394" s="4">
+        <f>E$246+J394+$N$374+$N$392</f>
+        <v>5.4199999999999998E-2</v>
+      </c>
+      <c r="G394" s="9">
+        <v>9.7100000000000006E-2</v>
+      </c>
+      <c r="H394" s="9">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="I394" s="9">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="J394" s="9">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L394" s="9"/>
+      <c r="N394" s="9"/>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A395" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B395" s="4">
+        <f t="shared" ref="B395" si="472">B$246+G395</f>
+        <v>0.2666</v>
+      </c>
+      <c r="C395" s="7">
+        <f t="shared" ref="C395" si="473">C$246+H395+$L$370</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="D395" s="7">
+        <f t="shared" ref="D395" si="474">D$246+I395</f>
+        <v>0.16059999999999999</v>
+      </c>
+      <c r="E395" s="4">
+        <f t="shared" ref="E395:E402" si="475">E$246+J395+$N$374+$N$392</f>
+        <v>5.62E-2</v>
+      </c>
+      <c r="G395" s="9">
+        <v>9.6699999999999994E-2</v>
+      </c>
+      <c r="H395" s="9">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="I395" s="9">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="J395" s="9">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="L395" s="9"/>
+      <c r="N395" s="9"/>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A396" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B396" s="4">
+        <f t="shared" ref="B396" si="476">B$246+G396</f>
+        <v>0.27010000000000001</v>
+      </c>
+      <c r="C396" s="7">
+        <f t="shared" ref="C396" si="477">C$246+H396+$L$370</f>
+        <v>0.21389999999999998</v>
+      </c>
+      <c r="D396" s="7">
+        <f t="shared" ref="D396" si="478">D$246+I396</f>
+        <v>0.1643</v>
+      </c>
+      <c r="E396" s="4">
+        <f t="shared" si="475"/>
+        <v>5.9399999999999994E-2</v>
+      </c>
+      <c r="G396" s="9">
+        <v>0.1002</v>
+      </c>
+      <c r="H396" s="9">
+        <v>7.7200000000000005E-2</v>
+      </c>
+      <c r="I396" s="9">
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="J396" s="9">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="L396" s="9"/>
+      <c r="N396" s="9"/>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A397" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B397" s="4">
+        <f t="shared" ref="B397" si="479">B$246+G397</f>
+        <v>0.2747</v>
+      </c>
+      <c r="C397" s="7">
+        <f t="shared" ref="C397" si="480">C$246+H397+$L$370</f>
+        <v>0.21649999999999997</v>
+      </c>
+      <c r="D397" s="7">
+        <f t="shared" ref="D397" si="481">D$246+I397</f>
+        <v>0.16949999999999998</v>
+      </c>
+      <c r="E397" s="4">
+        <f t="shared" si="475"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G397" s="9">
+        <v>0.1048</v>
+      </c>
+      <c r="H397" s="9">
+        <v>7.9799999999999996E-2</v>
+      </c>
+      <c r="I397" s="9">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="J397" s="9">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="L397" s="9"/>
+      <c r="N397" s="9"/>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A398" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B398" s="4">
+        <f t="shared" ref="B398" si="482">B$246+G398</f>
+        <v>0.27289999999999998</v>
+      </c>
+      <c r="C398" s="7">
+        <f t="shared" ref="C398" si="483">C$246+H398+$L$370</f>
+        <v>0.21739999999999998</v>
+      </c>
+      <c r="D398" s="7">
+        <f t="shared" ref="D398" si="484">D$246+I398</f>
+        <v>0.1651</v>
+      </c>
+      <c r="E398" s="4">
+        <f t="shared" si="475"/>
+        <v>6.2E-2</v>
+      </c>
+      <c r="G398" s="9">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="H398" s="9">
+        <v>8.0699999999999994E-2</v>
+      </c>
+      <c r="I398" s="9">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="J398" s="9">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="L398" s="9"/>
+      <c r="N398" s="9"/>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A399" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B399" s="4">
+        <f t="shared" ref="B399" si="485">B$246+G399</f>
+        <v>0.26729999999999998</v>
+      </c>
+      <c r="C399" s="7">
+        <f t="shared" ref="C399" si="486">C$246+H399+$L$370</f>
+        <v>0.2056</v>
+      </c>
+      <c r="D399" s="7">
+        <f t="shared" ref="D399" si="487">D$246+I399</f>
+        <v>0.15789999999999998</v>
+      </c>
+      <c r="E399" s="4">
+        <f t="shared" si="475"/>
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="G399" s="9">
+        <v>9.74E-2</v>
+      </c>
+      <c r="H399" s="9">
+        <v>6.8900000000000003E-2</v>
+      </c>
+      <c r="I399" s="9">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="J399" s="9">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="L399" s="9"/>
+      <c r="N399" s="9"/>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A400" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B400" s="4">
+        <f t="shared" ref="B400" si="488">B$246+G400</f>
+        <v>0.27239999999999998</v>
+      </c>
+      <c r="C400" s="7">
+        <f t="shared" ref="C400" si="489">C$246+H400+$L$370</f>
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="D400" s="7">
+        <f t="shared" ref="D400" si="490">D$246+I400</f>
+        <v>0.16289999999999999</v>
+      </c>
+      <c r="E400" s="4">
+        <f t="shared" si="475"/>
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="G400" s="9">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="H400" s="9">
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="I400" s="9">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="J400" s="9">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="L400" s="9"/>
+      <c r="N400" s="9"/>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A401" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B401" s="4">
+        <f t="shared" ref="B401" si="491">B$246+G401</f>
+        <v>0.26960000000000001</v>
+      </c>
+      <c r="C401" s="7">
+        <f t="shared" ref="C401" si="492">C$246+H401+$L$370</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="D401" s="7">
+        <f t="shared" ref="D401" si="493">D$246+I401</f>
+        <v>0.1578</v>
+      </c>
+      <c r="E401" s="4">
+        <f t="shared" si="475"/>
+        <v>5.4099999999999995E-2</v>
+      </c>
+      <c r="G401" s="9">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="H401" s="9">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="I401" s="9">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="J401" s="9">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="L401" s="9"/>
+      <c r="N401" s="9"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B402" s="4">
+        <f t="shared" ref="B402" si="494">B$246+G402</f>
+        <v>0.27229999999999999</v>
+      </c>
+      <c r="C402" s="7">
+        <f>C$246+H402+$L$370</f>
+        <v>0.21150000000000002</v>
+      </c>
+      <c r="D402" s="7">
+        <f t="shared" ref="D402" si="495">D$246+I402</f>
+        <v>0.16120000000000001</v>
+      </c>
+      <c r="E402" s="4">
+        <f>E$246+J402+$N$374+$N$392</f>
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="G402" s="9">
+        <v>0.1024</v>
+      </c>
+      <c r="H402" s="9">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="I402" s="9">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="J402" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="L402" s="9"/>
+      <c r="N402" s="9"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B403" s="4">
+        <f t="shared" ref="B403" si="496">B$246+G403</f>
+        <v>0.27090000000000003</v>
+      </c>
+      <c r="C403" s="7">
+        <f>C$246+H403+$L$370</f>
+        <v>0.20739999999999997</v>
+      </c>
+      <c r="D403" s="7">
+        <f t="shared" ref="D403" si="497">D$246+I403</f>
+        <v>0.1595</v>
+      </c>
+      <c r="E403" s="4">
+        <f>E$246+J403+$N$374+$N$392</f>
+        <v>5.5499999999999994E-2</v>
+      </c>
+      <c r="G403" s="9">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H403" s="9">
+        <v>7.0699999999999999E-2</v>
+      </c>
+      <c r="I403" s="9">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="J403" s="9">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="L403" s="9"/>
+      <c r="N403" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Hana_EMP.xlsx
+++ b/Hana_EMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\Codex\펀드차트\fund_returns_daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB24C665-8D59-47B5-AA30-26F64D6F3792}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E95F4B-BDD6-4186-8A42-87C5EAA325E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="15960" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:S403"/>
+  <dimension ref="A1:S404"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -8927,7 +8927,7 @@
         <v>0.24529999999999999</v>
       </c>
       <c r="C372" s="7">
-        <f t="shared" ref="C371:C381" si="400">C$246+H372+$L$370</f>
+        <f t="shared" ref="C372:C381" si="400">C$246+H372+$L$370</f>
         <v>0.18790000000000001</v>
       </c>
       <c r="D372" s="7">
@@ -9043,7 +9043,7 @@
         <v>0.14150000000000001</v>
       </c>
       <c r="E375" s="4">
-        <f t="shared" ref="E374:E381" si="410">E$246+J375+$N$374</f>
+        <f t="shared" ref="E375:E381" si="410">E$246+J375+$N$374</f>
         <v>4.5700000000000005E-2</v>
       </c>
       <c r="G375" s="9">
@@ -9747,7 +9747,7 @@
         <v>0.16059999999999999</v>
       </c>
       <c r="E395" s="4">
-        <f t="shared" ref="E395:E402" si="475">E$246+J395+$N$374+$N$392</f>
+        <f t="shared" ref="E395:E401" si="475">E$246+J395+$N$374+$N$392</f>
         <v>5.62E-2</v>
       </c>
       <c r="G395" s="9">
@@ -10044,6 +10044,41 @@
       </c>
       <c r="L403" s="9"/>
       <c r="N403" s="9"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B404" s="4">
+        <f t="shared" ref="B404" si="498">B$246+G404</f>
+        <v>0.27310000000000001</v>
+      </c>
+      <c r="C404" s="7">
+        <f>C$246+H404+$L$370</f>
+        <v>0.21250000000000002</v>
+      </c>
+      <c r="D404" s="7">
+        <f t="shared" ref="D404" si="499">D$246+I404</f>
+        <v>0.16550000000000001</v>
+      </c>
+      <c r="E404" s="4">
+        <f>E$246+J404+$N$374+$N$392</f>
+        <v>5.79E-2</v>
+      </c>
+      <c r="G404" s="9">
+        <v>0.1032</v>
+      </c>
+      <c r="H404" s="9">
+        <v>7.5800000000000006E-2</v>
+      </c>
+      <c r="I404" s="9">
+        <v>4.58E-2</v>
+      </c>
+      <c r="J404" s="9">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="L404" s="9"/>
+      <c r="N404" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
